--- a/gstdatabase/GSTR-1-2023-2024.xlsx
+++ b/gstdatabase/GSTR-1-2023-2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Jul-26\GST Statistics Downloads 31st Jul 26\Downloads\GSTR 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\GSTR 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A326D8-06CB-4999-B744-41CED5C78AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23C35BF6-2C0C-428B-B8BB-F3FCB8FEAA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,10 +183,10 @@
 CD</t>
   </si>
   <si>
-    <t>Data Considered upto 31st Jul 2026</t>
+    <t>Data Considered upto 31st Aug 2026</t>
   </si>
   <si>
-    <t>Filing %age as on 31st Jul 2026</t>
+    <t>Filing %age as on 31st Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -362,18 +362,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="7" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -385,6 +373,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="2" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -684,13 +684,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -702,10 +702,10 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="19"/>
+      <c r="B3" s="15"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -722,107 +722,107 @@
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
     </row>
     <row r="8" spans="1:62" s="9" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="18">
         <v>45017</v>
       </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="15">
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="18">
         <v>45047</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="16"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="15">
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="18">
         <v>45078</v>
       </c>
-      <c r="N8" s="16"/>
-      <c r="O8" s="16"/>
-      <c r="P8" s="16"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="15">
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="18">
         <v>45108</v>
       </c>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="17"/>
-      <c r="W8" s="15">
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="18">
         <v>45139</v>
       </c>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="17"/>
-      <c r="AB8" s="15">
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="20"/>
+      <c r="AB8" s="18">
         <v>45170</v>
       </c>
-      <c r="AC8" s="16"/>
-      <c r="AD8" s="16"/>
-      <c r="AE8" s="16"/>
-      <c r="AF8" s="17"/>
-      <c r="AG8" s="15">
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="19"/>
+      <c r="AE8" s="19"/>
+      <c r="AF8" s="20"/>
+      <c r="AG8" s="18">
         <v>45200</v>
       </c>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="16"/>
-      <c r="AJ8" s="16"/>
-      <c r="AK8" s="17"/>
-      <c r="AL8" s="15">
+      <c r="AH8" s="19"/>
+      <c r="AI8" s="19"/>
+      <c r="AJ8" s="19"/>
+      <c r="AK8" s="20"/>
+      <c r="AL8" s="18">
         <v>45231</v>
       </c>
-      <c r="AM8" s="16"/>
-      <c r="AN8" s="16"/>
-      <c r="AO8" s="16"/>
-      <c r="AP8" s="17"/>
-      <c r="AQ8" s="15">
+      <c r="AM8" s="19"/>
+      <c r="AN8" s="19"/>
+      <c r="AO8" s="19"/>
+      <c r="AP8" s="20"/>
+      <c r="AQ8" s="18">
         <v>45261</v>
       </c>
-      <c r="AR8" s="16"/>
-      <c r="AS8" s="16"/>
-      <c r="AT8" s="16"/>
-      <c r="AU8" s="17"/>
-      <c r="AV8" s="15">
+      <c r="AR8" s="19"/>
+      <c r="AS8" s="19"/>
+      <c r="AT8" s="19"/>
+      <c r="AU8" s="20"/>
+      <c r="AV8" s="18">
         <v>45292</v>
       </c>
-      <c r="AW8" s="16"/>
-      <c r="AX8" s="16"/>
-      <c r="AY8" s="16"/>
-      <c r="AZ8" s="17"/>
-      <c r="BA8" s="15">
+      <c r="AW8" s="19"/>
+      <c r="AX8" s="19"/>
+      <c r="AY8" s="19"/>
+      <c r="AZ8" s="20"/>
+      <c r="BA8" s="18">
         <v>45323</v>
       </c>
-      <c r="BB8" s="16"/>
-      <c r="BC8" s="16"/>
-      <c r="BD8" s="16"/>
-      <c r="BE8" s="17"/>
-      <c r="BF8" s="15">
+      <c r="BB8" s="19"/>
+      <c r="BC8" s="19"/>
+      <c r="BD8" s="19"/>
+      <c r="BE8" s="20"/>
+      <c r="BF8" s="18">
         <v>45352</v>
       </c>
-      <c r="BG8" s="16"/>
-      <c r="BH8" s="16"/>
-      <c r="BI8" s="16"/>
-      <c r="BJ8" s="17"/>
+      <c r="BG8" s="19"/>
+      <c r="BH8" s="19"/>
+      <c r="BI8" s="19"/>
+      <c r="BJ8" s="20"/>
     </row>
     <row r="9" spans="1:62" s="9" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="21"/>
-      <c r="B9" s="21"/>
+      <c r="A9" s="17"/>
+      <c r="B9" s="17"/>
       <c r="C9" s="12" t="s">
         <v>2</v>
       </c>
@@ -1053,14 +1053,14 @@
       </c>
       <c r="O10" s="3">
         <f>P10-N10</f>
-        <v>74872</v>
+        <v>74873</v>
       </c>
       <c r="P10" s="5">
-        <v>120495</v>
+        <v>120496</v>
       </c>
       <c r="Q10" s="4">
         <f>P10/M10</f>
-        <v>1.0002407318247473</v>
+        <v>1.0002490329221523</v>
       </c>
       <c r="R10" s="5">
         <v>70979</v>
@@ -1087,14 +1087,14 @@
       </c>
       <c r="Y10" s="3">
         <f>Z10-X10</f>
-        <v>42547</v>
+        <v>42549</v>
       </c>
       <c r="Z10" s="5">
-        <v>72937</v>
+        <v>72939</v>
       </c>
       <c r="AA10" s="4">
         <f>Z10/W10</f>
-        <v>0.99439657523040847</v>
+        <v>0.99442384250422644</v>
       </c>
       <c r="AB10" s="5">
         <v>123554</v>
@@ -1104,14 +1104,14 @@
       </c>
       <c r="AD10" s="3">
         <f>AE10-AC10</f>
-        <v>77026</v>
+        <v>77029</v>
       </c>
       <c r="AE10" s="5">
-        <v>123626</v>
+        <v>123629</v>
       </c>
       <c r="AF10" s="4">
         <f>AE10/AB10</f>
-        <v>1.0005827411496189</v>
+        <v>1.0006070220308529</v>
       </c>
       <c r="AG10" s="5">
         <v>71950</v>
@@ -1121,14 +1121,14 @@
       </c>
       <c r="AI10" s="3">
         <f>AJ10-AH10</f>
-        <v>41865</v>
+        <v>41867</v>
       </c>
       <c r="AJ10" s="5">
-        <v>71916</v>
+        <v>71918</v>
       </c>
       <c r="AK10" s="4">
         <f>AJ10/AG10</f>
-        <v>0.99952744961779016</v>
+        <v>0.99955524669909657</v>
       </c>
       <c r="AL10" s="5">
         <v>73532</v>
@@ -1138,14 +1138,14 @@
       </c>
       <c r="AN10" s="3">
         <f>AO10-AM10</f>
-        <v>43048</v>
+        <v>43053</v>
       </c>
       <c r="AO10" s="5">
-        <v>72978</v>
+        <v>72983</v>
       </c>
       <c r="AP10" s="4">
         <f>AO10/AL10</f>
-        <v>0.99246586520154489</v>
+        <v>0.99253386280802913</v>
       </c>
       <c r="AQ10" s="5">
         <v>125499</v>
@@ -1155,14 +1155,14 @@
       </c>
       <c r="AS10" s="3">
         <f>AT10-AR10</f>
-        <v>79256</v>
+        <v>79262</v>
       </c>
       <c r="AT10" s="5">
-        <v>125971</v>
+        <v>125977</v>
       </c>
       <c r="AU10" s="4">
         <f>AT10/AQ10</f>
-        <v>1.0037609861433159</v>
+        <v>1.0038087952892054</v>
       </c>
       <c r="AV10" s="5">
         <v>72481</v>
@@ -1172,14 +1172,14 @@
       </c>
       <c r="AX10" s="3">
         <f>AY10-AW10</f>
-        <v>42365</v>
+        <v>42370</v>
       </c>
       <c r="AY10" s="5">
-        <v>72229</v>
+        <v>72234</v>
       </c>
       <c r="AZ10" s="4">
         <f>AY10/AV10</f>
-        <v>0.99652322677667249</v>
+        <v>0.99659221037237344</v>
       </c>
       <c r="BA10" s="5">
         <v>73790</v>
@@ -1189,14 +1189,14 @@
       </c>
       <c r="BC10" s="3">
         <f>BD10-BB10</f>
-        <v>43035</v>
+        <v>43039</v>
       </c>
       <c r="BD10" s="5">
-        <v>73230</v>
+        <v>73234</v>
       </c>
       <c r="BE10" s="4">
         <f>BD10/BA10</f>
-        <v>0.99241089578533681</v>
+        <v>0.99246510367258434</v>
       </c>
       <c r="BF10" s="5">
         <v>128129</v>
@@ -1206,14 +1206,14 @@
       </c>
       <c r="BH10" s="3">
         <f>BI10-BG10</f>
-        <v>85647</v>
+        <v>85654</v>
       </c>
       <c r="BI10" s="5">
-        <v>128170</v>
+        <v>128177</v>
       </c>
       <c r="BJ10" s="4">
         <f>BI10/BF10</f>
-        <v>1.0003199900100679</v>
+        <v>1.0003746224508112</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.3">
@@ -1231,14 +1231,14 @@
       </c>
       <c r="E11" s="3">
         <f t="shared" ref="E11:E47" si="0">F11-D11</f>
-        <v>17635</v>
+        <v>17637</v>
       </c>
       <c r="F11" s="5">
-        <v>44790</v>
+        <v>44792</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" ref="G11:G47" si="1">F11/C11</f>
-        <v>1.0062002965359214</v>
+        <v>1.0062452262209642</v>
       </c>
       <c r="H11" s="5">
         <v>46110</v>
@@ -1248,14 +1248,14 @@
       </c>
       <c r="J11" s="3">
         <f t="shared" ref="J11:J33" si="2">K11-I11</f>
-        <v>18777</v>
+        <v>18778</v>
       </c>
       <c r="K11" s="5">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="L11" s="4">
         <f t="shared" ref="L11:L33" si="3">K11/H11</f>
-        <v>0.99759271307742359</v>
+        <v>0.99761440034699633</v>
       </c>
       <c r="M11" s="5">
         <v>102242</v>
@@ -1265,14 +1265,14 @@
       </c>
       <c r="O11" s="3">
         <f t="shared" ref="O11:O33" si="4">P11-N11</f>
-        <v>52510</v>
+        <v>52511</v>
       </c>
       <c r="P11" s="5">
-        <v>102573</v>
+        <v>102574</v>
       </c>
       <c r="Q11" s="4">
         <f t="shared" ref="Q11:Q33" si="5">P11/M11</f>
-        <v>1.0032374171084291</v>
+        <v>1.0032471978247688</v>
       </c>
       <c r="R11" s="5">
         <v>44890</v>
@@ -1282,14 +1282,14 @@
       </c>
       <c r="T11" s="3">
         <f t="shared" ref="T11:T33" si="6">U11-S11</f>
-        <v>16801</v>
+        <v>16802</v>
       </c>
       <c r="U11" s="5">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="V11" s="4">
         <f t="shared" ref="V11:V33" si="7">U11/R11</f>
-        <v>0.99857429271552689</v>
+        <v>0.99859656939184671</v>
       </c>
       <c r="W11" s="5">
         <v>46425</v>
@@ -1299,14 +1299,14 @@
       </c>
       <c r="Y11" s="3">
         <f t="shared" ref="Y11:Y33" si="8">Z11-X11</f>
-        <v>17311</v>
+        <v>17312</v>
       </c>
       <c r="Z11" s="5">
-        <v>45908</v>
+        <v>45909</v>
       </c>
       <c r="AA11" s="4">
         <f t="shared" ref="AA11:AA33" si="9">Z11/W11</f>
-        <v>0.98886375875067312</v>
+        <v>0.98888529886914378</v>
       </c>
       <c r="AB11" s="5">
         <v>103964</v>
@@ -1316,14 +1316,14 @@
       </c>
       <c r="AD11" s="3">
         <f t="shared" ref="AD11:AD33" si="10">AE11-AC11</f>
-        <v>44422</v>
+        <v>44425</v>
       </c>
       <c r="AE11" s="5">
-        <v>104344</v>
+        <v>104347</v>
       </c>
       <c r="AF11" s="4">
         <f t="shared" ref="AF11:AF33" si="11">AE11/AB11</f>
-        <v>1.0036551113847101</v>
+        <v>1.0036839675272209</v>
       </c>
       <c r="AG11" s="5">
         <v>45569</v>
@@ -1333,14 +1333,14 @@
       </c>
       <c r="AI11" s="3">
         <f t="shared" ref="AI11:AI33" si="12">AJ11-AH11</f>
-        <v>15645</v>
+        <v>15647</v>
       </c>
       <c r="AJ11" s="5">
-        <v>45354</v>
+        <v>45356</v>
       </c>
       <c r="AK11" s="4">
         <f t="shared" ref="AK11:AK33" si="13">AJ11/AG11</f>
-        <v>0.99528188022559194</v>
+        <v>0.99532576971186548</v>
       </c>
       <c r="AL11" s="5">
         <v>46951</v>
@@ -1350,14 +1350,14 @@
       </c>
       <c r="AN11" s="3">
         <f t="shared" ref="AN11:AN25" si="14">AO11-AM11</f>
-        <v>16015</v>
+        <v>16017</v>
       </c>
       <c r="AO11" s="5">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="AP11" s="4">
         <f t="shared" ref="AP11:AP26" si="15">AO11/AL11</f>
-        <v>0.98541032139890528</v>
+        <v>0.98545291900066023</v>
       </c>
       <c r="AQ11" s="5">
         <v>105644</v>
@@ -1367,14 +1367,14 @@
       </c>
       <c r="AS11" s="3">
         <f t="shared" ref="AS11:AS25" si="16">AT11-AR11</f>
-        <v>42448</v>
+        <v>42452</v>
       </c>
       <c r="AT11" s="5">
-        <v>106054</v>
+        <v>106058</v>
       </c>
       <c r="AU11" s="4">
         <f t="shared" ref="AU11:AU26" si="17">AT11/AQ11</f>
-        <v>1.0038809586914543</v>
+        <v>1.0039188217030783</v>
       </c>
       <c r="AV11" s="5">
         <v>46072</v>
@@ -1384,14 +1384,14 @@
       </c>
       <c r="AX11" s="3">
         <f t="shared" ref="AX11:AX25" si="18">AY11-AW11</f>
-        <v>15108</v>
+        <v>15110</v>
       </c>
       <c r="AY11" s="5">
-        <v>45953</v>
+        <v>45955</v>
       </c>
       <c r="AZ11" s="4">
         <f t="shared" ref="AZ11:AZ26" si="19">AY11/AV11</f>
-        <v>0.99741708629970482</v>
+        <v>0.9974604966139955</v>
       </c>
       <c r="BA11" s="5">
         <v>47252</v>
@@ -1401,14 +1401,14 @@
       </c>
       <c r="BC11" s="3">
         <f t="shared" ref="BC11:BC25" si="20">BD11-BB11</f>
-        <v>15574</v>
+        <v>15576</v>
       </c>
       <c r="BD11" s="5">
-        <v>46920</v>
+        <v>46922</v>
       </c>
       <c r="BE11" s="4">
         <f t="shared" ref="BE11:BE26" si="21">BD11/BA11</f>
-        <v>0.99297384237704223</v>
+        <v>0.99301616862778297</v>
       </c>
       <c r="BF11" s="5">
         <v>107665</v>
@@ -1418,14 +1418,14 @@
       </c>
       <c r="BH11" s="3">
         <f t="shared" ref="BH11:BH33" si="22">BI11-BG11</f>
-        <v>46587</v>
+        <v>46592</v>
       </c>
       <c r="BI11" s="5">
-        <v>107783</v>
+        <v>107788</v>
       </c>
       <c r="BJ11" s="4">
         <f t="shared" ref="BJ11:BJ33" si="23">BI11/BF11</f>
-        <v>1.0010959921980216</v>
+        <v>1.0011424325453955</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.3">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="E12" s="3">
         <f t="shared" si="0"/>
-        <v>35173</v>
+        <v>35177</v>
       </c>
       <c r="F12" s="5">
-        <v>165074</v>
+        <v>165078</v>
       </c>
       <c r="G12" s="4">
         <f t="shared" si="1"/>
-        <v>0.99460143399409529</v>
+        <v>0.99462553473519311</v>
       </c>
       <c r="H12" s="5">
         <v>170538</v>
@@ -1460,14 +1460,14 @@
       </c>
       <c r="J12" s="3">
         <f t="shared" si="2"/>
-        <v>37617</v>
+        <v>37621</v>
       </c>
       <c r="K12" s="5">
-        <v>168157</v>
+        <v>168161</v>
       </c>
       <c r="L12" s="4">
         <f t="shared" si="3"/>
-        <v>0.98603830231385381</v>
+        <v>0.98606175749686287</v>
       </c>
       <c r="M12" s="5">
         <v>344875</v>
@@ -1477,14 +1477,14 @@
       </c>
       <c r="O12" s="3">
         <f t="shared" si="4"/>
-        <v>96119</v>
+        <v>96123</v>
       </c>
       <c r="P12" s="5">
-        <v>343880</v>
+        <v>343884</v>
       </c>
       <c r="Q12" s="4">
         <f t="shared" si="5"/>
-        <v>0.9971148967017035</v>
+        <v>0.99712649510692275</v>
       </c>
       <c r="R12" s="5">
         <v>167705</v>
@@ -1494,14 +1494,14 @@
       </c>
       <c r="T12" s="3">
         <f t="shared" si="6"/>
-        <v>37672</v>
+        <v>37676</v>
       </c>
       <c r="U12" s="5">
-        <v>166810</v>
+        <v>166814</v>
       </c>
       <c r="V12" s="4">
         <f t="shared" si="7"/>
-        <v>0.99466324796517691</v>
+        <v>0.99468709937091915</v>
       </c>
       <c r="W12" s="5">
         <v>171864</v>
@@ -1511,14 +1511,14 @@
       </c>
       <c r="Y12" s="3">
         <f t="shared" si="8"/>
-        <v>38700</v>
+        <v>38704</v>
       </c>
       <c r="Z12" s="5">
-        <v>169940</v>
+        <v>169944</v>
       </c>
       <c r="AA12" s="4">
         <f t="shared" si="9"/>
-        <v>0.98880510170832747</v>
+        <v>0.98882837592515016</v>
       </c>
       <c r="AB12" s="5">
         <v>349048</v>
@@ -1528,14 +1528,14 @@
       </c>
       <c r="AD12" s="3">
         <f t="shared" si="10"/>
-        <v>93197</v>
+        <v>93201</v>
       </c>
       <c r="AE12" s="5">
-        <v>348651</v>
+        <v>348655</v>
       </c>
       <c r="AF12" s="4">
         <f t="shared" si="11"/>
-        <v>0.99886262061378372</v>
+        <v>0.99887408035571035</v>
       </c>
       <c r="AG12" s="5">
         <v>170526</v>
@@ -1545,14 +1545,14 @@
       </c>
       <c r="AI12" s="3">
         <f t="shared" si="12"/>
-        <v>38084</v>
+        <v>38087</v>
       </c>
       <c r="AJ12" s="5">
-        <v>169860</v>
+        <v>169863</v>
       </c>
       <c r="AK12" s="4">
         <f t="shared" si="13"/>
-        <v>0.99609443721192081</v>
+        <v>0.99611202983709224</v>
       </c>
       <c r="AL12" s="5">
         <v>174892</v>
@@ -1562,14 +1562,14 @@
       </c>
       <c r="AN12" s="3">
         <f t="shared" si="14"/>
-        <v>38327</v>
+        <v>38331</v>
       </c>
       <c r="AO12" s="5">
-        <v>172275</v>
+        <v>172279</v>
       </c>
       <c r="AP12" s="4">
         <f t="shared" si="15"/>
-        <v>0.98503647965601626</v>
+        <v>0.98505935091370678</v>
       </c>
       <c r="AQ12" s="5">
         <v>353589</v>
@@ -1579,14 +1579,14 @@
       </c>
       <c r="AS12" s="3">
         <f t="shared" si="16"/>
-        <v>94345</v>
+        <v>94350</v>
       </c>
       <c r="AT12" s="5">
-        <v>353364</v>
+        <v>353369</v>
       </c>
       <c r="AU12" s="4">
         <f t="shared" si="17"/>
-        <v>0.99936366798740917</v>
+        <v>0.9993778086988</v>
       </c>
       <c r="AV12" s="5">
         <v>172980</v>
@@ -1596,14 +1596,14 @@
       </c>
       <c r="AX12" s="3">
         <f t="shared" si="18"/>
-        <v>36205</v>
+        <v>36209</v>
       </c>
       <c r="AY12" s="5">
-        <v>171881</v>
+        <v>171885</v>
       </c>
       <c r="AZ12" s="4">
         <f t="shared" si="19"/>
-        <v>0.99364666435426063</v>
+        <v>0.99366978841484566</v>
       </c>
       <c r="BA12" s="5">
         <v>177212</v>
@@ -1613,14 +1613,14 @@
       </c>
       <c r="BC12" s="3">
         <f t="shared" si="20"/>
-        <v>36715</v>
+        <v>36719</v>
       </c>
       <c r="BD12" s="5">
-        <v>174609</v>
+        <v>174613</v>
       </c>
       <c r="BE12" s="4">
         <f t="shared" si="21"/>
-        <v>0.98531137846195516</v>
+        <v>0.98533395029681958</v>
       </c>
       <c r="BF12" s="5">
         <v>359260</v>
@@ -1630,14 +1630,14 @@
       </c>
       <c r="BH12" s="3">
         <f t="shared" si="22"/>
-        <v>100768</v>
+        <v>100772</v>
       </c>
       <c r="BI12" s="5">
-        <v>358008</v>
+        <v>358012</v>
       </c>
       <c r="BJ12" s="4">
         <f t="shared" si="23"/>
-        <v>0.99651505873183766</v>
+        <v>0.99652619272949949</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.3">
@@ -1867,14 +1867,14 @@
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>36557</v>
+        <v>36558</v>
       </c>
       <c r="F14" s="5">
-        <v>85001</v>
+        <v>85002</v>
       </c>
       <c r="G14" s="4">
         <f t="shared" si="1"/>
-        <v>0.99552604148366775</v>
+        <v>0.99553775341695649</v>
       </c>
       <c r="H14" s="5">
         <v>88261</v>
@@ -1884,14 +1884,14 @@
       </c>
       <c r="J14" s="3">
         <f t="shared" si="2"/>
-        <v>37986</v>
+        <v>37987</v>
       </c>
       <c r="K14" s="5">
-        <v>86811</v>
+        <v>86812</v>
       </c>
       <c r="L14" s="4">
         <f t="shared" si="3"/>
-        <v>0.98357145285006964</v>
+        <v>0.98358278288258683</v>
       </c>
       <c r="M14" s="5">
         <v>157146</v>
@@ -1901,14 +1901,14 @@
       </c>
       <c r="O14" s="3">
         <f t="shared" si="4"/>
-        <v>76995</v>
+        <v>76996</v>
       </c>
       <c r="P14" s="5">
-        <v>155896</v>
+        <v>155897</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="5"/>
-        <v>0.99204561363318189</v>
+        <v>0.99205197714227533</v>
       </c>
       <c r="R14" s="5">
         <v>86469</v>
@@ -1918,14 +1918,14 @@
       </c>
       <c r="T14" s="3">
         <f t="shared" si="6"/>
-        <v>36762</v>
+        <v>36763</v>
       </c>
       <c r="U14" s="5">
-        <v>85094</v>
+        <v>85095</v>
       </c>
       <c r="V14" s="4">
         <f t="shared" si="7"/>
-        <v>0.98409834738461177</v>
+        <v>0.98410991222287758</v>
       </c>
       <c r="W14" s="5">
         <v>88169</v>
@@ -1935,14 +1935,14 @@
       </c>
       <c r="Y14" s="3">
         <f t="shared" si="8"/>
-        <v>37745</v>
+        <v>37746</v>
       </c>
       <c r="Z14" s="5">
-        <v>86310</v>
+        <v>86311</v>
       </c>
       <c r="AA14" s="4">
         <f t="shared" si="9"/>
-        <v>0.97891549183953541</v>
+        <v>0.97892683369438238</v>
       </c>
       <c r="AB14" s="5">
         <v>157930</v>
@@ -1952,14 +1952,14 @@
       </c>
       <c r="AD14" s="3">
         <f t="shared" si="10"/>
-        <v>76156</v>
+        <v>76158</v>
       </c>
       <c r="AE14" s="5">
-        <v>157572</v>
+        <v>157574</v>
       </c>
       <c r="AF14" s="4">
         <f t="shared" si="11"/>
-        <v>0.99773317292471353</v>
+        <v>0.9977458367631229</v>
       </c>
       <c r="AG14" s="5">
         <v>87312</v>
@@ -1969,14 +1969,14 @@
       </c>
       <c r="AI14" s="3">
         <f t="shared" si="12"/>
-        <v>37775</v>
+        <v>37778</v>
       </c>
       <c r="AJ14" s="5">
-        <v>86631</v>
+        <v>86634</v>
       </c>
       <c r="AK14" s="4">
         <f t="shared" si="13"/>
-        <v>0.99220038482682793</v>
+        <v>0.99223474436503578</v>
       </c>
       <c r="AL14" s="5">
         <v>89337</v>
@@ -1986,14 +1986,14 @@
       </c>
       <c r="AN14" s="3">
         <f t="shared" si="14"/>
-        <v>37708</v>
+        <v>37710</v>
       </c>
       <c r="AO14" s="5">
-        <v>87826</v>
+        <v>87828</v>
       </c>
       <c r="AP14" s="4">
         <f t="shared" si="15"/>
-        <v>0.98308651510572331</v>
+        <v>0.98310890224654957</v>
       </c>
       <c r="AQ14" s="5">
         <v>160173</v>
@@ -2003,14 +2003,14 @@
       </c>
       <c r="AS14" s="3">
         <f t="shared" si="16"/>
-        <v>77660</v>
+        <v>77666</v>
       </c>
       <c r="AT14" s="5">
-        <v>160670</v>
+        <v>160676</v>
       </c>
       <c r="AU14" s="4">
         <f t="shared" si="17"/>
-        <v>1.0031028949947869</v>
+        <v>1.0031403544917059</v>
       </c>
       <c r="AV14" s="5">
         <v>88523</v>
@@ -2020,14 +2020,14 @@
       </c>
       <c r="AX14" s="3">
         <f t="shared" si="18"/>
-        <v>37639</v>
+        <v>37642</v>
       </c>
       <c r="AY14" s="5">
-        <v>88176</v>
+        <v>88179</v>
       </c>
       <c r="AZ14" s="4">
         <f t="shared" si="19"/>
-        <v>0.99608011477243197</v>
+        <v>0.99611400427007668</v>
       </c>
       <c r="BA14" s="5">
         <v>90782</v>
@@ -2037,14 +2037,14 @@
       </c>
       <c r="BC14" s="3">
         <f t="shared" si="20"/>
-        <v>37745</v>
+        <v>37749</v>
       </c>
       <c r="BD14" s="5">
-        <v>89659</v>
+        <v>89663</v>
       </c>
       <c r="BE14" s="4">
         <f t="shared" si="21"/>
-        <v>0.98762970632944858</v>
+        <v>0.98767376792756278</v>
       </c>
       <c r="BF14" s="5">
         <v>163900</v>
@@ -2054,14 +2054,14 @@
       </c>
       <c r="BH14" s="3">
         <f t="shared" si="22"/>
-        <v>82167</v>
+        <v>82175</v>
       </c>
       <c r="BI14" s="5">
-        <v>163321</v>
+        <v>163329</v>
       </c>
       <c r="BJ14" s="4">
         <f t="shared" si="23"/>
-        <v>0.99646735814521048</v>
+        <v>0.99651616839536306</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.3">
@@ -2164,14 +2164,14 @@
       </c>
       <c r="AD15" s="3">
         <f t="shared" si="10"/>
-        <v>142481</v>
+        <v>142483</v>
       </c>
       <c r="AE15" s="5">
-        <v>492169</v>
+        <v>492171</v>
       </c>
       <c r="AF15" s="4">
         <f t="shared" si="11"/>
-        <v>0.99290077629476603</v>
+        <v>0.99290481109084749</v>
       </c>
       <c r="AG15" s="5">
         <v>292071</v>
@@ -2181,14 +2181,14 @@
       </c>
       <c r="AI15" s="3">
         <f t="shared" si="12"/>
-        <v>78361</v>
+        <v>78362</v>
       </c>
       <c r="AJ15" s="5">
-        <v>289370</v>
+        <v>289371</v>
       </c>
       <c r="AK15" s="4">
         <f t="shared" si="13"/>
-        <v>0.99075224859708766</v>
+        <v>0.9907556724221166</v>
       </c>
       <c r="AL15" s="5">
         <v>298411</v>
@@ -2198,14 +2198,14 @@
       </c>
       <c r="AN15" s="3">
         <f t="shared" si="14"/>
-        <v>75048</v>
+        <v>75049</v>
       </c>
       <c r="AO15" s="5">
-        <v>293269</v>
+        <v>293270</v>
       </c>
       <c r="AP15" s="4">
         <f t="shared" si="15"/>
-        <v>0.98276873171565393</v>
+        <v>0.98277208279855632</v>
       </c>
       <c r="AQ15" s="5">
         <v>502913</v>
@@ -2215,14 +2215,14 @@
       </c>
       <c r="AS15" s="3">
         <f t="shared" si="16"/>
-        <v>137744</v>
+        <v>137747</v>
       </c>
       <c r="AT15" s="5">
-        <v>499832</v>
+        <v>499835</v>
       </c>
       <c r="AU15" s="4">
         <f t="shared" si="17"/>
-        <v>0.99387369187115859</v>
+        <v>0.99387965711763271</v>
       </c>
       <c r="AV15" s="5">
         <v>298012</v>
@@ -2232,14 +2232,14 @@
       </c>
       <c r="AX15" s="3">
         <f t="shared" si="18"/>
-        <v>71737</v>
+        <v>71738</v>
       </c>
       <c r="AY15" s="5">
-        <v>294440</v>
+        <v>294441</v>
       </c>
       <c r="AZ15" s="4">
         <f t="shared" si="19"/>
-        <v>0.9880139054803162</v>
+        <v>0.98801726104989063</v>
       </c>
       <c r="BA15" s="5">
         <v>303376</v>
@@ -2249,14 +2249,14 @@
       </c>
       <c r="BC15" s="3">
         <f t="shared" si="20"/>
-        <v>71599</v>
+        <v>71602</v>
       </c>
       <c r="BD15" s="5">
-        <v>298827</v>
+        <v>298830</v>
       </c>
       <c r="BE15" s="4">
         <f t="shared" si="21"/>
-        <v>0.98500540583302565</v>
+        <v>0.98501529455197512</v>
       </c>
       <c r="BF15" s="5">
         <v>511329</v>
@@ -2266,14 +2266,14 @@
       </c>
       <c r="BH15" s="3">
         <f t="shared" si="22"/>
-        <v>149701</v>
+        <v>149707</v>
       </c>
       <c r="BI15" s="5">
-        <v>507707</v>
+        <v>507713</v>
       </c>
       <c r="BJ15" s="4">
         <f t="shared" si="23"/>
-        <v>0.99291649798857484</v>
+        <v>0.99292823211669978</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.3">
@@ -2291,14 +2291,14 @@
       </c>
       <c r="E16" s="3">
         <f t="shared" si="0"/>
-        <v>107231</v>
+        <v>107238</v>
       </c>
       <c r="F16" s="5">
-        <v>426865</v>
+        <v>426872</v>
       </c>
       <c r="G16" s="4">
         <f t="shared" si="1"/>
-        <v>0.99124548631671838</v>
+        <v>0.99126174138191281</v>
       </c>
       <c r="H16" s="5">
         <v>441093</v>
@@ -2308,14 +2308,14 @@
       </c>
       <c r="J16" s="3">
         <f t="shared" si="2"/>
-        <v>113348</v>
+        <v>113356</v>
       </c>
       <c r="K16" s="5">
-        <v>431274</v>
+        <v>431282</v>
       </c>
       <c r="L16" s="4">
         <f t="shared" si="3"/>
-        <v>0.97773938829226492</v>
+        <v>0.97775752505707414</v>
       </c>
       <c r="M16" s="5">
         <v>754668</v>
@@ -2325,14 +2325,14 @@
       </c>
       <c r="O16" s="3">
         <f t="shared" si="4"/>
-        <v>199886</v>
+        <v>199897</v>
       </c>
       <c r="P16" s="5">
-        <v>751738</v>
+        <v>751749</v>
       </c>
       <c r="Q16" s="4">
         <f t="shared" si="5"/>
-        <v>0.99611749802562188</v>
+        <v>0.99613207397160075</v>
       </c>
       <c r="R16" s="5">
         <v>429537</v>
@@ -2342,14 +2342,14 @@
       </c>
       <c r="T16" s="3">
         <f t="shared" si="6"/>
-        <v>111577</v>
+        <v>111585</v>
       </c>
       <c r="U16" s="5">
-        <v>423879</v>
+        <v>423887</v>
       </c>
       <c r="V16" s="4">
         <f t="shared" si="7"/>
-        <v>0.98682767724317111</v>
+        <v>0.98684630194837697</v>
       </c>
       <c r="W16" s="5">
         <v>433887</v>
@@ -2359,14 +2359,14 @@
       </c>
       <c r="Y16" s="3">
         <f t="shared" si="8"/>
-        <v>112655</v>
+        <v>112663</v>
       </c>
       <c r="Z16" s="5">
-        <v>426898</v>
+        <v>426906</v>
       </c>
       <c r="AA16" s="4">
         <f t="shared" si="9"/>
-        <v>0.98389211937670407</v>
+        <v>0.98391055735709987</v>
       </c>
       <c r="AB16" s="5">
         <v>753330</v>
@@ -2376,14 +2376,14 @@
       </c>
       <c r="AD16" s="3">
         <f t="shared" si="10"/>
-        <v>200078</v>
+        <v>200097</v>
       </c>
       <c r="AE16" s="5">
-        <v>752156</v>
+        <v>752175</v>
       </c>
       <c r="AF16" s="4">
         <f t="shared" si="11"/>
-        <v>0.99844158602471689</v>
+        <v>0.99846680737525384</v>
       </c>
       <c r="AG16" s="5">
         <v>431686</v>
@@ -2393,14 +2393,14 @@
       </c>
       <c r="AI16" s="3">
         <f t="shared" si="12"/>
-        <v>113817</v>
+        <v>113831</v>
       </c>
       <c r="AJ16" s="5">
-        <v>426158</v>
+        <v>426172</v>
       </c>
       <c r="AK16" s="4">
         <f t="shared" si="13"/>
-        <v>0.98719439592666891</v>
+        <v>0.98722682690659413</v>
       </c>
       <c r="AL16" s="5">
         <v>438911</v>
@@ -2410,14 +2410,14 @@
       </c>
       <c r="AN16" s="3">
         <f t="shared" si="14"/>
-        <v>114085</v>
+        <v>114099</v>
       </c>
       <c r="AO16" s="5">
-        <v>430577</v>
+        <v>430591</v>
       </c>
       <c r="AP16" s="4">
         <f t="shared" si="15"/>
-        <v>0.98101209584631055</v>
+        <v>0.98104399297351852</v>
       </c>
       <c r="AQ16" s="5">
         <v>759875</v>
@@ -2427,14 +2427,14 @@
       </c>
       <c r="AS16" s="3">
         <f t="shared" si="16"/>
-        <v>195703</v>
+        <v>195728</v>
       </c>
       <c r="AT16" s="5">
-        <v>758702</v>
+        <v>758727</v>
       </c>
       <c r="AU16" s="4">
         <f t="shared" si="17"/>
-        <v>0.99845632505346271</v>
+        <v>0.9984892252015134</v>
       </c>
       <c r="AV16" s="5">
         <v>437477</v>
@@ -2444,14 +2444,14 @@
       </c>
       <c r="AX16" s="3">
         <f t="shared" si="18"/>
-        <v>108389</v>
+        <v>108404</v>
       </c>
       <c r="AY16" s="5">
-        <v>431130</v>
+        <v>431145</v>
       </c>
       <c r="AZ16" s="4">
         <f t="shared" si="19"/>
-        <v>0.98549180871222941</v>
+        <v>0.98552609622905885</v>
       </c>
       <c r="BA16" s="5">
         <v>445887</v>
@@ -2461,14 +2461,14 @@
       </c>
       <c r="BC16" s="3">
         <f t="shared" si="20"/>
-        <v>109813</v>
+        <v>109828</v>
       </c>
       <c r="BD16" s="5">
-        <v>436981</v>
+        <v>436996</v>
       </c>
       <c r="BE16" s="4">
         <f t="shared" si="21"/>
-        <v>0.98002632954089264</v>
+        <v>0.98005997035123249</v>
       </c>
       <c r="BF16" s="5">
         <v>770088</v>
@@ -2478,14 +2478,14 @@
       </c>
       <c r="BH16" s="3">
         <f t="shared" si="22"/>
-        <v>207460</v>
+        <v>207496</v>
       </c>
       <c r="BI16" s="5">
-        <v>765042</v>
+        <v>765078</v>
       </c>
       <c r="BJ16" s="4">
         <f t="shared" si="23"/>
-        <v>0.99344750210365573</v>
+        <v>0.99349425000779135</v>
       </c>
     </row>
     <row r="17" spans="1:62" x14ac:dyDescent="0.3">
@@ -2503,14 +2503,14 @@
       </c>
       <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="F17" s="5">
-        <v>301162</v>
+        <v>301164</v>
       </c>
       <c r="G17" s="4">
         <f t="shared" si="1"/>
-        <v>0.99533337299305291</v>
+        <v>0.99533998294632053</v>
       </c>
       <c r="H17" s="5">
         <v>314962</v>
@@ -2520,14 +2520,14 @@
       </c>
       <c r="J17" s="3">
         <f t="shared" si="2"/>
-        <v>92357</v>
+        <v>92360</v>
       </c>
       <c r="K17" s="5">
-        <v>309408</v>
+        <v>309411</v>
       </c>
       <c r="L17" s="4">
         <f t="shared" si="3"/>
-        <v>0.9823661267073488</v>
+        <v>0.98237565166591523</v>
       </c>
       <c r="M17" s="5">
         <v>695415</v>
@@ -2537,14 +2537,14 @@
       </c>
       <c r="O17" s="3">
         <f t="shared" si="4"/>
-        <v>249502</v>
+        <v>249507</v>
       </c>
       <c r="P17" s="5">
-        <v>691781</v>
+        <v>691786</v>
       </c>
       <c r="Q17" s="4">
         <f t="shared" si="5"/>
-        <v>0.99477434337769532</v>
+        <v>0.99478153332901931</v>
       </c>
       <c r="R17" s="5">
         <v>305324</v>
@@ -2554,14 +2554,14 @@
       </c>
       <c r="T17" s="3">
         <f t="shared" si="6"/>
-        <v>90718</v>
+        <v>90722</v>
       </c>
       <c r="U17" s="5">
-        <v>302704</v>
+        <v>302708</v>
       </c>
       <c r="V17" s="4">
         <f t="shared" si="7"/>
-        <v>0.99141895167101179</v>
+        <v>0.99143205250815525</v>
       </c>
       <c r="W17" s="5">
         <v>316716</v>
@@ -2571,14 +2571,14 @@
       </c>
       <c r="Y17" s="3">
         <f t="shared" si="8"/>
-        <v>93462</v>
+        <v>93466</v>
       </c>
       <c r="Z17" s="5">
-        <v>309815</v>
+        <v>309819</v>
       </c>
       <c r="AA17" s="4">
         <f t="shared" si="9"/>
-        <v>0.9782107629548239</v>
+        <v>0.97822339256621071</v>
       </c>
       <c r="AB17" s="5">
         <v>703511</v>
@@ -2588,14 +2588,14 @@
       </c>
       <c r="AD17" s="3">
         <f t="shared" si="10"/>
-        <v>254117</v>
+        <v>254125</v>
       </c>
       <c r="AE17" s="5">
-        <v>699792</v>
+        <v>699800</v>
       </c>
       <c r="AF17" s="4">
         <f t="shared" si="11"/>
-        <v>0.99471365764003694</v>
+        <v>0.99472502917509464</v>
       </c>
       <c r="AG17" s="5">
         <v>311084</v>
@@ -2605,14 +2605,14 @@
       </c>
       <c r="AI17" s="3">
         <f t="shared" si="12"/>
-        <v>90898</v>
+        <v>90903</v>
       </c>
       <c r="AJ17" s="5">
-        <v>308992</v>
+        <v>308997</v>
       </c>
       <c r="AK17" s="4">
         <f t="shared" si="13"/>
-        <v>0.99327512826117703</v>
+        <v>0.99329120109038072</v>
       </c>
       <c r="AL17" s="5">
         <v>323550</v>
@@ -2622,14 +2622,14 @@
       </c>
       <c r="AN17" s="3">
         <f t="shared" si="14"/>
-        <v>93548</v>
+        <v>93554</v>
       </c>
       <c r="AO17" s="5">
-        <v>316293</v>
+        <v>316299</v>
       </c>
       <c r="AP17" s="4">
         <f t="shared" si="15"/>
-        <v>0.97757070004636071</v>
+        <v>0.97758924432081595</v>
       </c>
       <c r="AQ17" s="5">
         <v>714257</v>
@@ -2639,14 +2639,14 @@
       </c>
       <c r="AS17" s="3">
         <f t="shared" si="16"/>
-        <v>244294</v>
+        <v>244309</v>
       </c>
       <c r="AT17" s="5">
-        <v>714218</v>
+        <v>714233</v>
       </c>
       <c r="AU17" s="4">
         <f t="shared" si="17"/>
-        <v>0.99994539780499181</v>
+        <v>0.99996639864922565</v>
       </c>
       <c r="AV17" s="5">
         <v>316308</v>
@@ -2656,14 +2656,14 @@
       </c>
       <c r="AX17" s="3">
         <f t="shared" si="18"/>
-        <v>87078</v>
+        <v>87085</v>
       </c>
       <c r="AY17" s="5">
-        <v>314734</v>
+        <v>314741</v>
       </c>
       <c r="AZ17" s="4">
         <f t="shared" si="19"/>
-        <v>0.99502383752544987</v>
+        <v>0.99504596785411692</v>
       </c>
       <c r="BA17" s="5">
         <v>328067</v>
@@ -2673,14 +2673,14 @@
       </c>
       <c r="BC17" s="3">
         <f t="shared" si="20"/>
-        <v>88504</v>
+        <v>88510</v>
       </c>
       <c r="BD17" s="5">
-        <v>321674</v>
+        <v>321680</v>
       </c>
       <c r="BE17" s="4">
         <f t="shared" si="21"/>
-        <v>0.98051312689176295</v>
+        <v>0.98053141583883785</v>
       </c>
       <c r="BF17" s="5">
         <v>726752</v>
@@ -2690,14 +2690,14 @@
       </c>
       <c r="BH17" s="3">
         <f t="shared" si="22"/>
-        <v>273154</v>
+        <v>273173</v>
       </c>
       <c r="BI17" s="5">
-        <v>725624</v>
+        <v>725643</v>
       </c>
       <c r="BJ17" s="4">
         <f t="shared" si="23"/>
-        <v>0.99844788868830081</v>
+        <v>0.99847403240720356</v>
       </c>
     </row>
     <row r="18" spans="1:62" x14ac:dyDescent="0.3">
@@ -2732,14 +2732,14 @@
       </c>
       <c r="J18" s="3">
         <f t="shared" si="2"/>
-        <v>449519</v>
+        <v>449520</v>
       </c>
       <c r="K18" s="5">
-        <v>932549</v>
+        <v>932550</v>
       </c>
       <c r="L18" s="4">
         <f t="shared" si="3"/>
-        <v>0.98864365218110362</v>
+        <v>0.98864471233306583</v>
       </c>
       <c r="M18" s="5">
         <v>1440086</v>
@@ -2749,14 +2749,14 @@
       </c>
       <c r="O18" s="3">
         <f t="shared" si="4"/>
-        <v>736568</v>
+        <v>736571</v>
       </c>
       <c r="P18" s="5">
-        <v>1430658</v>
+        <v>1430661</v>
       </c>
       <c r="Q18" s="4">
         <f t="shared" si="5"/>
-        <v>0.9934531687690874</v>
+        <v>0.99345525197800688</v>
       </c>
       <c r="R18" s="5">
         <v>938677</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="T18" s="3">
         <f t="shared" si="6"/>
-        <v>455701</v>
+        <v>455706</v>
       </c>
       <c r="U18" s="5">
-        <v>928268</v>
+        <v>928273</v>
       </c>
       <c r="V18" s="4">
         <f t="shared" si="7"/>
-        <v>0.98891098855090731</v>
+        <v>0.98891631519681422</v>
       </c>
       <c r="W18" s="5">
         <v>958009</v>
@@ -2783,14 +2783,14 @@
       </c>
       <c r="Y18" s="3">
         <f t="shared" si="8"/>
-        <v>462188</v>
+        <v>462197</v>
       </c>
       <c r="Z18" s="5">
-        <v>943368</v>
+        <v>943377</v>
       </c>
       <c r="AA18" s="4">
         <f t="shared" si="9"/>
-        <v>0.98471726257268977</v>
+        <v>0.98472665705645768</v>
       </c>
       <c r="AB18" s="5">
         <v>1463397</v>
@@ -2800,14 +2800,14 @@
       </c>
       <c r="AD18" s="3">
         <f t="shared" si="10"/>
-        <v>751175</v>
+        <v>751191</v>
       </c>
       <c r="AE18" s="5">
-        <v>1454933</v>
+        <v>1454949</v>
       </c>
       <c r="AF18" s="4">
         <f t="shared" si="11"/>
-        <v>0.99421619697184016</v>
+        <v>0.99422713043692179</v>
       </c>
       <c r="AG18" s="5">
         <v>959088</v>
@@ -2817,14 +2817,14 @@
       </c>
       <c r="AI18" s="3">
         <f t="shared" si="12"/>
-        <v>469108</v>
+        <v>469123</v>
       </c>
       <c r="AJ18" s="5">
-        <v>951079</v>
+        <v>951094</v>
       </c>
       <c r="AK18" s="4">
         <f t="shared" si="13"/>
-        <v>0.99164935855729608</v>
+        <v>0.99166499841516109</v>
       </c>
       <c r="AL18" s="5">
         <v>980581</v>
@@ -2834,14 +2834,14 @@
       </c>
       <c r="AN18" s="3">
         <f t="shared" si="14"/>
-        <v>470105</v>
+        <v>470122</v>
       </c>
       <c r="AO18" s="5">
-        <v>964126</v>
+        <v>964143</v>
       </c>
       <c r="AP18" s="4">
         <f t="shared" si="15"/>
-        <v>0.98321913233073044</v>
+        <v>0.98323646899134287</v>
       </c>
       <c r="AQ18" s="5">
         <v>1490329</v>
@@ -2851,14 +2851,14 @@
       </c>
       <c r="AS18" s="3">
         <f t="shared" si="16"/>
-        <v>753021</v>
+        <v>753048</v>
       </c>
       <c r="AT18" s="5">
-        <v>1486004</v>
+        <v>1486031</v>
       </c>
       <c r="AU18" s="4">
         <f t="shared" si="17"/>
-        <v>0.99709795622308894</v>
+        <v>0.99711607302817029</v>
       </c>
       <c r="AV18" s="5">
         <v>983291</v>
@@ -2868,14 +2868,14 @@
       </c>
       <c r="AX18" s="3">
         <f t="shared" si="18"/>
-        <v>464904</v>
+        <v>464925</v>
       </c>
       <c r="AY18" s="5">
-        <v>974202</v>
+        <v>974223</v>
       </c>
       <c r="AZ18" s="4">
         <f t="shared" si="19"/>
-        <v>0.99075655121423867</v>
+        <v>0.99077790806587263</v>
       </c>
       <c r="BA18" s="5">
         <v>1002255</v>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="BC18" s="3">
         <f t="shared" si="20"/>
-        <v>473173</v>
+        <v>473197</v>
       </c>
       <c r="BD18" s="5">
-        <v>987686</v>
+        <v>987710</v>
       </c>
       <c r="BE18" s="4">
         <f t="shared" si="21"/>
-        <v>0.98546377917795369</v>
+        <v>0.98548772517971972</v>
       </c>
       <c r="BF18" s="5">
         <v>1522890</v>
@@ -2902,14 +2902,14 @@
       </c>
       <c r="BH18" s="3">
         <f t="shared" si="22"/>
-        <v>809237</v>
+        <v>809277</v>
       </c>
       <c r="BI18" s="5">
-        <v>1512856</v>
+        <v>1512896</v>
       </c>
       <c r="BJ18" s="4">
         <f t="shared" si="23"/>
-        <v>0.99341121157798662</v>
+        <v>0.99343747742778532</v>
       </c>
     </row>
     <row r="19" spans="1:62" x14ac:dyDescent="0.3">
@@ -2927,14 +2927,14 @@
       </c>
       <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>185666</v>
+        <v>185671</v>
       </c>
       <c r="F19" s="5">
-        <v>271130</v>
+        <v>271135</v>
       </c>
       <c r="G19" s="4">
         <f t="shared" si="1"/>
-        <v>0.9852286560438962</v>
+        <v>0.98524682497865146</v>
       </c>
       <c r="H19" s="5">
         <v>285702</v>
@@ -2944,14 +2944,14 @@
       </c>
       <c r="J19" s="3">
         <f t="shared" si="2"/>
-        <v>189618</v>
+        <v>189624</v>
       </c>
       <c r="K19" s="5">
-        <v>277226</v>
+        <v>277232</v>
       </c>
       <c r="L19" s="4">
         <f t="shared" si="3"/>
-        <v>0.97033272430714523</v>
+        <v>0.97035372521018404</v>
       </c>
       <c r="M19" s="5">
         <v>479092</v>
@@ -2961,14 +2961,14 @@
       </c>
       <c r="O19" s="3">
         <f t="shared" si="4"/>
-        <v>327931</v>
+        <v>327939</v>
       </c>
       <c r="P19" s="5">
-        <v>470329</v>
+        <v>470337</v>
       </c>
       <c r="Q19" s="4">
         <f t="shared" si="5"/>
-        <v>0.98170914980838753</v>
+        <v>0.981725848062585</v>
       </c>
       <c r="R19" s="5">
         <v>279649</v>
@@ -2978,14 +2978,14 @@
       </c>
       <c r="T19" s="3">
         <f t="shared" si="6"/>
-        <v>185551</v>
+        <v>185557</v>
       </c>
       <c r="U19" s="5">
-        <v>272368</v>
+        <v>272374</v>
       </c>
       <c r="V19" s="4">
         <f t="shared" si="7"/>
-        <v>0.97396379032286906</v>
+        <v>0.97398524579025847</v>
       </c>
       <c r="W19" s="5">
         <v>287758</v>
@@ -2995,14 +2995,14 @@
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="8"/>
-        <v>188443</v>
+        <v>188450</v>
       </c>
       <c r="Z19" s="5">
-        <v>276673</v>
+        <v>276680</v>
       </c>
       <c r="AA19" s="4">
         <f t="shared" si="9"/>
-        <v>0.96147804752604615</v>
+        <v>0.9615023735221957</v>
       </c>
       <c r="AB19" s="5">
         <v>485015</v>
@@ -3012,14 +3012,14 @@
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="10"/>
-        <v>331904</v>
+        <v>331920</v>
       </c>
       <c r="AE19" s="5">
-        <v>476462</v>
+        <v>476478</v>
       </c>
       <c r="AF19" s="4">
         <f t="shared" si="11"/>
-        <v>0.9823654938507056</v>
+        <v>0.98239848252115913</v>
       </c>
       <c r="AG19" s="5">
         <v>283525</v>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="AI19" s="3">
         <f t="shared" si="12"/>
-        <v>184072</v>
+        <v>184086</v>
       </c>
       <c r="AJ19" s="5">
-        <v>276464</v>
+        <v>276478</v>
       </c>
       <c r="AK19" s="4">
         <f t="shared" si="13"/>
-        <v>0.97509567057578694</v>
+        <v>0.97514504893748344</v>
       </c>
       <c r="AL19" s="5">
         <v>295027</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="AN19" s="3">
         <f t="shared" si="14"/>
-        <v>188122</v>
+        <v>188138</v>
       </c>
       <c r="AO19" s="5">
-        <v>282068</v>
+        <v>282084</v>
       </c>
       <c r="AP19" s="4">
         <f t="shared" si="15"/>
-        <v>0.9560752066759991</v>
+        <v>0.95612943900049829</v>
       </c>
       <c r="AQ19" s="5">
         <v>494059</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="AS19" s="3">
         <f t="shared" si="16"/>
-        <v>335797</v>
+        <v>335822</v>
       </c>
       <c r="AT19" s="5">
-        <v>487936</v>
+        <v>487961</v>
       </c>
       <c r="AU19" s="4">
         <f t="shared" si="17"/>
-        <v>0.98760674332417786</v>
+        <v>0.9876573445681589</v>
       </c>
       <c r="AV19" s="5">
         <v>287237</v>
@@ -3080,14 +3080,14 @@
       </c>
       <c r="AX19" s="3">
         <f t="shared" si="18"/>
-        <v>186037</v>
+        <v>186052</v>
       </c>
       <c r="AY19" s="5">
-        <v>283027</v>
+        <v>283042</v>
       </c>
       <c r="AZ19" s="4">
         <f t="shared" si="19"/>
-        <v>0.98534311387460527</v>
+        <v>0.98539533555913761</v>
       </c>
       <c r="BA19" s="5">
         <v>298081</v>
@@ -3097,14 +3097,14 @@
       </c>
       <c r="BC19" s="3">
         <f t="shared" si="20"/>
-        <v>191268</v>
+        <v>191284</v>
       </c>
       <c r="BD19" s="5">
-        <v>287460</v>
+        <v>287476</v>
       </c>
       <c r="BE19" s="4">
         <f t="shared" si="21"/>
-        <v>0.96436874540812734</v>
+        <v>0.96442242209332363</v>
       </c>
       <c r="BF19" s="5">
         <v>503654</v>
@@ -3114,14 +3114,14 @@
       </c>
       <c r="BH19" s="3">
         <f t="shared" si="22"/>
-        <v>355520</v>
+        <v>355560</v>
       </c>
       <c r="BI19" s="5">
-        <v>494104</v>
+        <v>494144</v>
       </c>
       <c r="BJ19" s="4">
         <f t="shared" si="23"/>
-        <v>0.98103857012949369</v>
+        <v>0.98111798973104547</v>
       </c>
     </row>
     <row r="20" spans="1:62" x14ac:dyDescent="0.3">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>3536</v>
+        <v>3537</v>
       </c>
       <c r="F20" s="5">
-        <v>5792</v>
+        <v>5793</v>
       </c>
       <c r="G20" s="4">
         <f t="shared" si="1"/>
-        <v>1.0262225372076541</v>
+        <v>1.0263997165131113</v>
       </c>
       <c r="H20" s="5">
         <v>5914</v>
@@ -3156,14 +3156,14 @@
       </c>
       <c r="J20" s="3">
         <f t="shared" si="2"/>
-        <v>3643</v>
+        <v>3644</v>
       </c>
       <c r="K20" s="5">
-        <v>5956</v>
+        <v>5957</v>
       </c>
       <c r="L20" s="4">
         <f t="shared" si="3"/>
-        <v>1.0071017923571186</v>
+        <v>1.0072708826513359</v>
       </c>
       <c r="M20" s="5">
         <v>9037</v>
@@ -3173,14 +3173,14 @@
       </c>
       <c r="O20" s="3">
         <f t="shared" si="4"/>
-        <v>5723</v>
+        <v>5724</v>
       </c>
       <c r="P20" s="5">
-        <v>9290</v>
+        <v>9291</v>
       </c>
       <c r="Q20" s="4">
         <f t="shared" si="5"/>
-        <v>1.0279960163771162</v>
+        <v>1.0281066725683301</v>
       </c>
       <c r="R20" s="5">
         <v>5910</v>
@@ -3190,14 +3190,14 @@
       </c>
       <c r="T20" s="3">
         <f t="shared" si="6"/>
-        <v>3640</v>
+        <v>3641</v>
       </c>
       <c r="U20" s="5">
-        <v>6027</v>
+        <v>6028</v>
       </c>
       <c r="V20" s="4">
         <f t="shared" si="7"/>
-        <v>1.0197969543147207</v>
+        <v>1.0199661590524534</v>
       </c>
       <c r="W20" s="5">
         <v>6115</v>
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Y20" s="3">
         <f t="shared" si="8"/>
-        <v>3723</v>
+        <v>3724</v>
       </c>
       <c r="Z20" s="5">
-        <v>6128</v>
+        <v>6129</v>
       </c>
       <c r="AA20" s="4">
         <f t="shared" si="9"/>
-        <v>1.0021259198691741</v>
+        <v>1.0022894521668029</v>
       </c>
       <c r="AB20" s="5">
         <v>9431</v>
@@ -3224,14 +3224,14 @@
       </c>
       <c r="AD20" s="3">
         <f t="shared" si="10"/>
-        <v>5787</v>
+        <v>5788</v>
       </c>
       <c r="AE20" s="5">
-        <v>9560</v>
+        <v>9561</v>
       </c>
       <c r="AF20" s="4">
         <f t="shared" si="11"/>
-        <v>1.0136782949846252</v>
+        <v>1.0137843282790797</v>
       </c>
       <c r="AG20" s="5">
         <v>6099</v>
@@ -3241,14 +3241,14 @@
       </c>
       <c r="AI20" s="3">
         <f t="shared" si="12"/>
-        <v>3560</v>
+        <v>3561</v>
       </c>
       <c r="AJ20" s="5">
-        <v>6150</v>
+        <v>6151</v>
       </c>
       <c r="AK20" s="4">
         <f t="shared" si="13"/>
-        <v>1.0083620265617315</v>
+        <v>1.0085259878668633</v>
       </c>
       <c r="AL20" s="5">
         <v>6250</v>
@@ -3258,14 +3258,14 @@
       </c>
       <c r="AN20" s="3">
         <f t="shared" si="14"/>
-        <v>3434</v>
+        <v>3435</v>
       </c>
       <c r="AO20" s="5">
-        <v>6232</v>
+        <v>6233</v>
       </c>
       <c r="AP20" s="4">
         <f t="shared" si="15"/>
-        <v>0.99712000000000001</v>
+        <v>0.99728000000000006</v>
       </c>
       <c r="AQ20" s="5">
         <v>9632</v>
@@ -3275,14 +3275,14 @@
       </c>
       <c r="AS20" s="3">
         <f t="shared" si="16"/>
-        <v>5970</v>
+        <v>5971</v>
       </c>
       <c r="AT20" s="5">
-        <v>9745</v>
+        <v>9746</v>
       </c>
       <c r="AU20" s="4">
         <f t="shared" si="17"/>
-        <v>1.0117317275747508</v>
+        <v>1.0118355481727574</v>
       </c>
       <c r="AV20" s="5">
         <v>6297</v>
@@ -3292,14 +3292,14 @@
       </c>
       <c r="AX20" s="3">
         <f t="shared" si="18"/>
-        <v>3623</v>
+        <v>3625</v>
       </c>
       <c r="AY20" s="5">
-        <v>6250</v>
+        <v>6252</v>
       </c>
       <c r="AZ20" s="4">
         <f t="shared" si="19"/>
-        <v>0.99253612831507065</v>
+        <v>0.99285373987613146</v>
       </c>
       <c r="BA20" s="5">
         <v>6366</v>
@@ -3309,14 +3309,14 @@
       </c>
       <c r="BC20" s="3">
         <f t="shared" si="20"/>
-        <v>3728</v>
+        <v>3731</v>
       </c>
       <c r="BD20" s="5">
-        <v>6292</v>
+        <v>6295</v>
       </c>
       <c r="BE20" s="4">
         <f t="shared" si="21"/>
-        <v>0.98837574615142942</v>
+        <v>0.98884699968583101</v>
       </c>
       <c r="BF20" s="5">
         <v>9853</v>
@@ -3326,14 +3326,14 @@
       </c>
       <c r="BH20" s="3">
         <f t="shared" si="22"/>
-        <v>6361</v>
+        <v>6364</v>
       </c>
       <c r="BI20" s="5">
-        <v>9898</v>
+        <v>9901</v>
       </c>
       <c r="BJ20" s="4">
         <f t="shared" si="23"/>
-        <v>1.0045671369126155</v>
+        <v>1.0048716127067898</v>
       </c>
     </row>
     <row r="21" spans="1:62" x14ac:dyDescent="0.3">
@@ -3351,14 +3351,14 @@
       </c>
       <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>7624</v>
+        <v>7626</v>
       </c>
       <c r="F21" s="5">
-        <v>9841</v>
+        <v>9843</v>
       </c>
       <c r="G21" s="4">
         <f t="shared" si="1"/>
-        <v>1.0282102183679867</v>
+        <v>1.0284191829484903</v>
       </c>
       <c r="H21" s="5">
         <v>10057</v>
@@ -3368,14 +3368,14 @@
       </c>
       <c r="J21" s="3">
         <f t="shared" si="2"/>
-        <v>7266</v>
+        <v>7268</v>
       </c>
       <c r="K21" s="5">
-        <v>9983</v>
+        <v>9985</v>
       </c>
       <c r="L21" s="4">
         <f t="shared" si="3"/>
-        <v>0.99264194093666103</v>
+        <v>0.99284080739783231</v>
       </c>
       <c r="M21" s="5">
         <v>12982</v>
@@ -3385,14 +3385,14 @@
       </c>
       <c r="O21" s="3">
         <f t="shared" si="4"/>
-        <v>9815</v>
+        <v>9817</v>
       </c>
       <c r="P21" s="5">
-        <v>13259</v>
+        <v>13261</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="5"/>
-        <v>1.0213372361731627</v>
+        <v>1.021491295640117</v>
       </c>
       <c r="R21" s="5">
         <v>9811</v>
@@ -3402,14 +3402,14 @@
       </c>
       <c r="T21" s="3">
         <f t="shared" si="6"/>
-        <v>7332</v>
+        <v>7334</v>
       </c>
       <c r="U21" s="5">
-        <v>10046</v>
+        <v>10048</v>
       </c>
       <c r="V21" s="4">
         <f t="shared" si="7"/>
-        <v>1.0239527061461624</v>
+        <v>1.0241565589644277</v>
       </c>
       <c r="W21" s="5">
         <v>10152</v>
@@ -3419,14 +3419,14 @@
       </c>
       <c r="Y21" s="3">
         <f t="shared" si="8"/>
-        <v>7389</v>
+        <v>7392</v>
       </c>
       <c r="Z21" s="5">
-        <v>10180</v>
+        <v>10183</v>
       </c>
       <c r="AA21" s="4">
         <f t="shared" si="9"/>
-        <v>1.0027580772261624</v>
+        <v>1.0030535855003939</v>
       </c>
       <c r="AB21" s="5">
         <v>13231</v>
@@ -3436,14 +3436,14 @@
       </c>
       <c r="AD21" s="3">
         <f t="shared" si="10"/>
-        <v>9739</v>
+        <v>9742</v>
       </c>
       <c r="AE21" s="5">
-        <v>13583</v>
+        <v>13586</v>
       </c>
       <c r="AF21" s="4">
         <f t="shared" si="11"/>
-        <v>1.0266041871362708</v>
+        <v>1.026830927367546</v>
       </c>
       <c r="AG21" s="5">
         <v>10040</v>
@@ -3453,14 +3453,14 @@
       </c>
       <c r="AI21" s="3">
         <f t="shared" si="12"/>
-        <v>7399</v>
+        <v>7402</v>
       </c>
       <c r="AJ21" s="5">
-        <v>10253</v>
+        <v>10256</v>
       </c>
       <c r="AK21" s="4">
         <f t="shared" si="13"/>
-        <v>1.0212151394422311</v>
+        <v>1.0215139442231076</v>
       </c>
       <c r="AL21" s="5">
         <v>10211</v>
@@ -3470,14 +3470,14 @@
       </c>
       <c r="AN21" s="3">
         <f t="shared" si="14"/>
-        <v>7526</v>
+        <v>7529</v>
       </c>
       <c r="AO21" s="5">
-        <v>10405</v>
+        <v>10408</v>
       </c>
       <c r="AP21" s="4">
         <f t="shared" si="15"/>
-        <v>1.0189991185975908</v>
+        <v>1.0192929194006464</v>
       </c>
       <c r="AQ21" s="5">
         <v>13473</v>
@@ -3487,14 +3487,14 @@
       </c>
       <c r="AS21" s="3">
         <f t="shared" si="16"/>
-        <v>10098</v>
+        <v>10101</v>
       </c>
       <c r="AT21" s="5">
-        <v>13912</v>
+        <v>13915</v>
       </c>
       <c r="AU21" s="4">
         <f t="shared" si="17"/>
-        <v>1.032583685890299</v>
+        <v>1.0328063534476359</v>
       </c>
       <c r="AV21" s="5">
         <v>10213</v>
@@ -3504,14 +3504,14 @@
       </c>
       <c r="AX21" s="3">
         <f t="shared" si="18"/>
-        <v>7710</v>
+        <v>7714</v>
       </c>
       <c r="AY21" s="5">
-        <v>10514</v>
+        <v>10518</v>
       </c>
       <c r="AZ21" s="4">
         <f t="shared" si="19"/>
-        <v>1.0294722412611377</v>
+        <v>1.0298638989523157</v>
       </c>
       <c r="BA21" s="5">
         <v>10449</v>
@@ -3521,14 +3521,14 @@
       </c>
       <c r="BC21" s="3">
         <f t="shared" si="20"/>
-        <v>7818</v>
+        <v>7822</v>
       </c>
       <c r="BD21" s="5">
-        <v>10656</v>
+        <v>10660</v>
       </c>
       <c r="BE21" s="4">
         <f t="shared" si="21"/>
-        <v>1.0198105081826012</v>
+        <v>1.020193319934922</v>
       </c>
       <c r="BF21" s="5">
         <v>13925</v>
@@ -3538,14 +3538,14 @@
       </c>
       <c r="BH21" s="3">
         <f t="shared" si="22"/>
-        <v>10908</v>
+        <v>10914</v>
       </c>
       <c r="BI21" s="5">
-        <v>14356</v>
+        <v>14362</v>
       </c>
       <c r="BJ21" s="4">
         <f t="shared" si="23"/>
-        <v>1.0309515260323159</v>
+        <v>1.0313824057450629</v>
       </c>
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.3">
@@ -3563,14 +3563,14 @@
       </c>
       <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>4203</v>
+        <v>4204</v>
       </c>
       <c r="F22" s="5">
-        <v>6231</v>
+        <v>6232</v>
       </c>
       <c r="G22" s="4">
         <f t="shared" si="1"/>
-        <v>1.0116902094495859</v>
+        <v>1.011852573469719</v>
       </c>
       <c r="H22" s="5">
         <v>6265</v>
@@ -3580,14 +3580,14 @@
       </c>
       <c r="J22" s="3">
         <f t="shared" si="2"/>
-        <v>4374</v>
+        <v>4376</v>
       </c>
       <c r="K22" s="5">
-        <v>6317</v>
+        <v>6319</v>
       </c>
       <c r="L22" s="4">
         <f t="shared" si="3"/>
-        <v>1.0083000798084596</v>
+        <v>1.0086193136472466</v>
       </c>
       <c r="M22" s="5">
         <v>7537</v>
@@ -3597,14 +3597,14 @@
       </c>
       <c r="O22" s="3">
         <f t="shared" si="4"/>
-        <v>5109</v>
+        <v>5111</v>
       </c>
       <c r="P22" s="5">
-        <v>7617</v>
+        <v>7619</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="5"/>
-        <v>1.0106143027729866</v>
+        <v>1.0108796603423114</v>
       </c>
       <c r="R22" s="5">
         <v>6306</v>
@@ -3614,14 +3614,14 @@
       </c>
       <c r="T22" s="3">
         <f t="shared" si="6"/>
-        <v>4411</v>
+        <v>4414</v>
       </c>
       <c r="U22" s="5">
-        <v>6369</v>
+        <v>6372</v>
       </c>
       <c r="V22" s="4">
         <f t="shared" si="7"/>
-        <v>1.0099904852521409</v>
+        <v>1.0104662226451</v>
       </c>
       <c r="W22" s="5">
         <v>6435</v>
@@ -3631,14 +3631,14 @@
       </c>
       <c r="Y22" s="3">
         <f t="shared" si="8"/>
-        <v>4401</v>
+        <v>4404</v>
       </c>
       <c r="Z22" s="5">
-        <v>6443</v>
+        <v>6446</v>
       </c>
       <c r="AA22" s="4">
         <f t="shared" si="9"/>
-        <v>1.0012432012432013</v>
+        <v>1.0017094017094017</v>
       </c>
       <c r="AB22" s="5">
         <v>7668</v>
@@ -3648,14 +3648,14 @@
       </c>
       <c r="AD22" s="3">
         <f t="shared" si="10"/>
-        <v>5300</v>
+        <v>5303</v>
       </c>
       <c r="AE22" s="5">
-        <v>7727</v>
+        <v>7730</v>
       </c>
       <c r="AF22" s="4">
         <f t="shared" si="11"/>
-        <v>1.0076943140323422</v>
+        <v>1.0080855503390715</v>
       </c>
       <c r="AG22" s="5">
         <v>6422</v>
@@ -3665,14 +3665,14 @@
       </c>
       <c r="AI22" s="3">
         <f t="shared" si="12"/>
-        <v>4410</v>
+        <v>4415</v>
       </c>
       <c r="AJ22" s="5">
-        <v>6462</v>
+        <v>6467</v>
       </c>
       <c r="AK22" s="4">
         <f t="shared" si="13"/>
-        <v>1.0062285892245406</v>
+        <v>1.0070071628776083</v>
       </c>
       <c r="AL22" s="5">
         <v>6508</v>
@@ -3682,14 +3682,14 @@
       </c>
       <c r="AN22" s="3">
         <f t="shared" si="14"/>
-        <v>4431</v>
+        <v>4437</v>
       </c>
       <c r="AO22" s="5">
-        <v>6511</v>
+        <v>6517</v>
       </c>
       <c r="AP22" s="4">
         <f t="shared" si="15"/>
-        <v>1.000460971112477</v>
+        <v>1.0013829133374308</v>
       </c>
       <c r="AQ22" s="5">
         <v>7781</v>
@@ -3699,14 +3699,14 @@
       </c>
       <c r="AS22" s="3">
         <f t="shared" si="16"/>
-        <v>5404</v>
+        <v>5410</v>
       </c>
       <c r="AT22" s="5">
-        <v>7820</v>
+        <v>7826</v>
       </c>
       <c r="AU22" s="4">
         <f t="shared" si="17"/>
-        <v>1.0050122092276057</v>
+        <v>1.005783318339545</v>
       </c>
       <c r="AV22" s="5">
         <v>6603</v>
@@ -3716,14 +3716,14 @@
       </c>
       <c r="AX22" s="3">
         <f t="shared" si="18"/>
-        <v>4481</v>
+        <v>4487</v>
       </c>
       <c r="AY22" s="5">
-        <v>6525</v>
+        <v>6531</v>
       </c>
       <c r="AZ22" s="4">
         <f t="shared" si="19"/>
-        <v>0.98818718764198088</v>
+        <v>0.98909586551567474</v>
       </c>
       <c r="BA22" s="5">
         <v>6608</v>
@@ -3733,14 +3733,14 @@
       </c>
       <c r="BC22" s="3">
         <f t="shared" si="20"/>
-        <v>4421</v>
+        <v>4426</v>
       </c>
       <c r="BD22" s="5">
-        <v>6566</v>
+        <v>6571</v>
       </c>
       <c r="BE22" s="4">
         <f t="shared" si="21"/>
-        <v>0.99364406779661019</v>
+        <v>0.99440072639225185</v>
       </c>
       <c r="BF22" s="5">
         <v>7906</v>
@@ -3750,14 +3750,14 @@
       </c>
       <c r="BH22" s="3">
         <f t="shared" si="22"/>
-        <v>5615</v>
+        <v>5620</v>
       </c>
       <c r="BI22" s="5">
-        <v>7963</v>
+        <v>7968</v>
       </c>
       <c r="BJ22" s="4">
         <f t="shared" si="23"/>
-        <v>1.0072097141411587</v>
+        <v>1.0078421452061725</v>
       </c>
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.3">
@@ -3775,14 +3775,14 @@
       </c>
       <c r="E23" s="3">
         <f t="shared" si="0"/>
-        <v>7376</v>
+        <v>7377</v>
       </c>
       <c r="F23" s="5">
-        <v>8495</v>
+        <v>8496</v>
       </c>
       <c r="G23" s="4">
         <f t="shared" si="1"/>
-        <v>0.96534090909090908</v>
+        <v>0.96545454545454545</v>
       </c>
       <c r="H23" s="5">
         <v>8763</v>
@@ -3792,14 +3792,14 @@
       </c>
       <c r="J23" s="3">
         <f t="shared" si="2"/>
-        <v>7010</v>
+        <v>7011</v>
       </c>
       <c r="K23" s="5">
-        <v>8528</v>
+        <v>8529</v>
       </c>
       <c r="L23" s="4">
         <f t="shared" si="3"/>
-        <v>0.97318269998858842</v>
+        <v>0.97329681615884966</v>
       </c>
       <c r="M23" s="5">
         <v>10654</v>
@@ -3809,14 +3809,14 @@
       </c>
       <c r="O23" s="3">
         <f t="shared" si="4"/>
-        <v>8131</v>
+        <v>8132</v>
       </c>
       <c r="P23" s="5">
-        <v>10516</v>
+        <v>10517</v>
       </c>
       <c r="Q23" s="4">
         <f t="shared" si="5"/>
-        <v>0.98704711845316317</v>
+        <v>0.98714097991364746</v>
       </c>
       <c r="R23" s="5">
         <v>8621</v>
@@ -3826,14 +3826,14 @@
       </c>
       <c r="T23" s="3">
         <f t="shared" si="6"/>
-        <v>6407</v>
+        <v>6408</v>
       </c>
       <c r="U23" s="5">
-        <v>8396</v>
+        <v>8397</v>
       </c>
       <c r="V23" s="4">
         <f t="shared" si="7"/>
-        <v>0.97390093956617563</v>
+        <v>0.97401693539032597</v>
       </c>
       <c r="W23" s="5">
         <v>8774</v>
@@ -3843,14 +3843,14 @@
       </c>
       <c r="Y23" s="3">
         <f t="shared" si="8"/>
-        <v>6297</v>
+        <v>6298</v>
       </c>
       <c r="Z23" s="5">
-        <v>8453</v>
+        <v>8454</v>
       </c>
       <c r="AA23" s="4">
         <f t="shared" si="9"/>
-        <v>0.96341463414634143</v>
+        <v>0.96352860724868927</v>
       </c>
       <c r="AB23" s="5">
         <v>10734</v>
@@ -3860,14 +3860,14 @@
       </c>
       <c r="AD23" s="3">
         <f t="shared" si="10"/>
-        <v>7679</v>
+        <v>7680</v>
       </c>
       <c r="AE23" s="5">
-        <v>10584</v>
+        <v>10585</v>
       </c>
       <c r="AF23" s="4">
         <f t="shared" si="11"/>
-        <v>0.98602571268865291</v>
+        <v>0.98611887460406189</v>
       </c>
       <c r="AG23" s="5">
         <v>8589</v>
@@ -3877,14 +3877,14 @@
       </c>
       <c r="AI23" s="3">
         <f t="shared" si="12"/>
-        <v>6127</v>
+        <v>6128</v>
       </c>
       <c r="AJ23" s="5">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="AK23" s="4">
         <f t="shared" si="13"/>
-        <v>0.98381650948888111</v>
+        <v>0.98393293747816979</v>
       </c>
       <c r="AL23" s="5">
         <v>8660</v>
@@ -3894,14 +3894,14 @@
       </c>
       <c r="AN23" s="3">
         <f t="shared" si="14"/>
-        <v>5951</v>
+        <v>5952</v>
       </c>
       <c r="AO23" s="5">
-        <v>8525</v>
+        <v>8526</v>
       </c>
       <c r="AP23" s="4">
         <f t="shared" si="15"/>
-        <v>0.98441108545034639</v>
+        <v>0.98452655889145502</v>
       </c>
       <c r="AQ23" s="5">
         <v>10698</v>
@@ -3911,14 +3911,14 @@
       </c>
       <c r="AS23" s="3">
         <f t="shared" si="16"/>
-        <v>7650</v>
+        <v>7651</v>
       </c>
       <c r="AT23" s="5">
-        <v>10757</v>
+        <v>10758</v>
       </c>
       <c r="AU23" s="4">
         <f t="shared" si="17"/>
-        <v>1.0055150495419705</v>
+        <v>1.0056085249579361</v>
       </c>
       <c r="AV23" s="5">
         <v>8445</v>
@@ -3928,14 +3928,14 @@
       </c>
       <c r="AX23" s="3">
         <f t="shared" si="18"/>
-        <v>6087</v>
+        <v>6089</v>
       </c>
       <c r="AY23" s="5">
-        <v>8507</v>
+        <v>8509</v>
       </c>
       <c r="AZ23" s="4">
         <f t="shared" si="19"/>
-        <v>1.0073416222616933</v>
+        <v>1.007578448786264</v>
       </c>
       <c r="BA23" s="5">
         <v>8623</v>
@@ -3945,14 +3945,14 @@
       </c>
       <c r="BC23" s="3">
         <f t="shared" si="20"/>
-        <v>6005</v>
+        <v>6007</v>
       </c>
       <c r="BD23" s="5">
-        <v>8554</v>
+        <v>8556</v>
       </c>
       <c r="BE23" s="4">
         <f t="shared" si="21"/>
-        <v>0.99199814449727475</v>
+        <v>0.99223008233793342</v>
       </c>
       <c r="BF23" s="5">
         <v>11023</v>
@@ -3962,14 +3962,14 @@
       </c>
       <c r="BH23" s="3">
         <f t="shared" si="22"/>
-        <v>7966</v>
+        <v>7968</v>
       </c>
       <c r="BI23" s="5">
-        <v>10944</v>
+        <v>10946</v>
       </c>
       <c r="BJ23" s="4">
         <f t="shared" si="23"/>
-        <v>0.99283316701442437</v>
+        <v>0.99301460582418577</v>
       </c>
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.3">
@@ -4089,14 +4089,14 @@
       </c>
       <c r="AI24" s="3">
         <f t="shared" si="12"/>
-        <v>4623</v>
+        <v>4624</v>
       </c>
       <c r="AJ24" s="5">
-        <v>5955</v>
+        <v>5956</v>
       </c>
       <c r="AK24" s="4">
         <f t="shared" si="13"/>
-        <v>0.98008558262014478</v>
+        <v>0.98025016458196179</v>
       </c>
       <c r="AL24" s="5">
         <v>6181</v>
@@ -4106,14 +4106,14 @@
       </c>
       <c r="AN24" s="3">
         <f t="shared" si="14"/>
-        <v>4441</v>
+        <v>4442</v>
       </c>
       <c r="AO24" s="5">
-        <v>6020</v>
+        <v>6021</v>
       </c>
       <c r="AP24" s="4">
         <f t="shared" si="15"/>
-        <v>0.97395243488108718</v>
+        <v>0.97411422099983824</v>
       </c>
       <c r="AQ24" s="5">
         <v>6974</v>
@@ -4123,14 +4123,14 @@
       </c>
       <c r="AS24" s="3">
         <f t="shared" si="16"/>
-        <v>5471</v>
+        <v>5472</v>
       </c>
       <c r="AT24" s="5">
-        <v>6911</v>
+        <v>6912</v>
       </c>
       <c r="AU24" s="4">
         <f t="shared" si="17"/>
-        <v>0.99096644680240897</v>
+        <v>0.99110983653570406</v>
       </c>
       <c r="AV24" s="5">
         <v>6124</v>
@@ -4140,14 +4140,14 @@
       </c>
       <c r="AX24" s="3">
         <f t="shared" si="18"/>
-        <v>4700</v>
+        <v>4701</v>
       </c>
       <c r="AY24" s="5">
-        <v>6047</v>
+        <v>6048</v>
       </c>
       <c r="AZ24" s="4">
         <f t="shared" si="19"/>
-        <v>0.98742651861528408</v>
+        <v>0.98758981058131945</v>
       </c>
       <c r="BA24" s="5">
         <v>6202</v>
@@ -4157,14 +4157,14 @@
       </c>
       <c r="BC24" s="3">
         <f t="shared" si="20"/>
-        <v>4730</v>
+        <v>4731</v>
       </c>
       <c r="BD24" s="5">
-        <v>6139</v>
+        <v>6140</v>
       </c>
       <c r="BE24" s="4">
         <f t="shared" si="21"/>
-        <v>0.98984198645598198</v>
+        <v>0.9900032247662045</v>
       </c>
       <c r="BF24" s="5">
         <v>7084</v>
@@ -4174,14 +4174,14 @@
       </c>
       <c r="BH24" s="3">
         <f t="shared" si="22"/>
-        <v>5556</v>
+        <v>5558</v>
       </c>
       <c r="BI24" s="5">
-        <v>7042</v>
+        <v>7044</v>
       </c>
       <c r="BJ24" s="4">
         <f t="shared" si="23"/>
-        <v>0.99407114624505932</v>
+        <v>0.99435347261434215</v>
       </c>
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.3">
@@ -4199,14 +4199,14 @@
       </c>
       <c r="E25" s="3">
         <f t="shared" si="0"/>
-        <v>10073</v>
+        <v>10074</v>
       </c>
       <c r="F25" s="5">
-        <v>18495</v>
+        <v>18496</v>
       </c>
       <c r="G25" s="4">
         <f t="shared" si="1"/>
-        <v>1.0115401443885363</v>
+        <v>1.0115948370159702</v>
       </c>
       <c r="H25" s="5">
         <v>18682</v>
@@ -4216,14 +4216,14 @@
       </c>
       <c r="J25" s="3">
         <f t="shared" si="2"/>
-        <v>10338</v>
+        <v>10339</v>
       </c>
       <c r="K25" s="5">
-        <v>18849</v>
+        <v>18850</v>
       </c>
       <c r="L25" s="4">
         <f t="shared" si="3"/>
-        <v>1.0089390857509903</v>
+        <v>1.0089926132105771</v>
       </c>
       <c r="M25" s="5">
         <v>25970</v>
@@ -4233,14 +4233,14 @@
       </c>
       <c r="O25" s="3">
         <f t="shared" si="4"/>
-        <v>14497</v>
+        <v>14499</v>
       </c>
       <c r="P25" s="5">
-        <v>26281</v>
+        <v>26283</v>
       </c>
       <c r="Q25" s="4">
         <f t="shared" si="5"/>
-        <v>1.0119753561802078</v>
+        <v>1.0120523681170581</v>
       </c>
       <c r="R25" s="5">
         <v>18895</v>
@@ -4250,14 +4250,14 @@
       </c>
       <c r="T25" s="3">
         <f t="shared" si="6"/>
-        <v>10407</v>
+        <v>10408</v>
       </c>
       <c r="U25" s="5">
-        <v>19049</v>
+        <v>19050</v>
       </c>
       <c r="V25" s="4">
         <f t="shared" si="7"/>
-        <v>1.0081503043133104</v>
+        <v>1.008203228367293</v>
       </c>
       <c r="W25" s="5">
         <v>19436</v>
@@ -4267,14 +4267,14 @@
       </c>
       <c r="Y25" s="3">
         <f t="shared" si="8"/>
-        <v>10769</v>
+        <v>10770</v>
       </c>
       <c r="Z25" s="5">
-        <v>19339</v>
+        <v>19340</v>
       </c>
       <c r="AA25" s="4">
         <f t="shared" si="9"/>
-        <v>0.99500926116484878</v>
+        <v>0.99506071208067504</v>
       </c>
       <c r="AB25" s="5">
         <v>26661</v>
@@ -4284,14 +4284,14 @@
       </c>
       <c r="AD25" s="3">
         <f t="shared" si="10"/>
-        <v>14626</v>
+        <v>14627</v>
       </c>
       <c r="AE25" s="5">
-        <v>26883</v>
+        <v>26884</v>
       </c>
       <c r="AF25" s="4">
         <f t="shared" si="11"/>
-        <v>1.0083267694385056</v>
+        <v>1.0083642774089494</v>
       </c>
       <c r="AG25" s="5">
         <v>19440</v>
@@ -4301,14 +4301,14 @@
       </c>
       <c r="AI25" s="3">
         <f t="shared" si="12"/>
-        <v>10487</v>
+        <v>10489</v>
       </c>
       <c r="AJ25" s="5">
-        <v>19517</v>
+        <v>19519</v>
       </c>
       <c r="AK25" s="4">
         <f t="shared" si="13"/>
-        <v>1.0039609053497942</v>
+        <v>1.0040637860082304</v>
       </c>
       <c r="AL25" s="5">
         <v>19709</v>
@@ -4318,14 +4318,14 @@
       </c>
       <c r="AN25" s="3">
         <f t="shared" si="14"/>
-        <v>10534</v>
+        <v>10536</v>
       </c>
       <c r="AO25" s="5">
-        <v>19693</v>
+        <v>19695</v>
       </c>
       <c r="AP25" s="4">
         <f t="shared" si="15"/>
-        <v>0.99918818813739918</v>
+        <v>0.99928966462022428</v>
       </c>
       <c r="AQ25" s="5">
         <v>27081</v>
@@ -4335,14 +4335,14 @@
       </c>
       <c r="AS25" s="3">
         <f t="shared" si="16"/>
-        <v>15504</v>
+        <v>15506</v>
       </c>
       <c r="AT25" s="5">
-        <v>27318</v>
+        <v>27320</v>
       </c>
       <c r="AU25" s="4">
         <f t="shared" si="17"/>
-        <v>1.0087515232081534</v>
+        <v>1.0088253757246779</v>
       </c>
       <c r="AV25" s="5">
         <v>19795</v>
@@ -4352,14 +4352,14 @@
       </c>
       <c r="AX25" s="3">
         <f t="shared" si="18"/>
-        <v>10841</v>
+        <v>10843</v>
       </c>
       <c r="AY25" s="5">
-        <v>19926</v>
+        <v>19928</v>
       </c>
       <c r="AZ25" s="4">
         <f t="shared" si="19"/>
-        <v>1.0066178327860571</v>
+        <v>1.0067188684011115</v>
       </c>
       <c r="BA25" s="5">
         <v>20139</v>
@@ -4369,14 +4369,14 @@
       </c>
       <c r="BC25" s="3">
         <f t="shared" si="20"/>
-        <v>11100</v>
+        <v>11103</v>
       </c>
       <c r="BD25" s="5">
-        <v>20151</v>
+        <v>20154</v>
       </c>
       <c r="BE25" s="4">
         <f t="shared" si="21"/>
-        <v>1.0005958587814687</v>
+        <v>1.0007448234768359</v>
       </c>
       <c r="BF25" s="5">
         <v>27639</v>
@@ -4386,14 +4386,14 @@
       </c>
       <c r="BH25" s="3">
         <f t="shared" si="22"/>
-        <v>16942</v>
+        <v>16945</v>
       </c>
       <c r="BI25" s="5">
-        <v>27812</v>
+        <v>27815</v>
       </c>
       <c r="BJ25" s="4">
         <f t="shared" si="23"/>
-        <v>1.0062592713195122</v>
+        <v>1.0063678135967293</v>
       </c>
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.3">
@@ -4411,14 +4411,14 @@
       </c>
       <c r="E26" s="3">
         <f t="shared" si="0"/>
-        <v>8946</v>
+        <v>8949</v>
       </c>
       <c r="F26" s="5">
-        <v>13324</v>
+        <v>13327</v>
       </c>
       <c r="G26" s="4">
         <f t="shared" si="1"/>
-        <v>0.98441078684891026</v>
+        <v>0.98463243442925752</v>
       </c>
       <c r="H26" s="5">
         <v>13884</v>
@@ -4428,14 +4428,14 @@
       </c>
       <c r="J26" s="3">
         <f t="shared" si="2"/>
-        <v>9413</v>
+        <v>9417</v>
       </c>
       <c r="K26" s="5">
-        <v>13919</v>
+        <v>13923</v>
       </c>
       <c r="L26" s="4">
         <f t="shared" si="3"/>
-        <v>1.0025208873523481</v>
+        <v>1.002808988764045</v>
       </c>
       <c r="M26" s="5">
         <v>25920</v>
@@ -4445,14 +4445,14 @@
       </c>
       <c r="O26" s="3">
         <f t="shared" si="4"/>
-        <v>17770</v>
+        <v>17777</v>
       </c>
       <c r="P26" s="5">
-        <v>26349</v>
+        <v>26356</v>
       </c>
       <c r="Q26" s="4">
         <f t="shared" si="5"/>
-        <v>1.016550925925926</v>
+        <v>1.0168209876543211</v>
       </c>
       <c r="R26" s="5">
         <v>13869</v>
@@ -4462,14 +4462,14 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="6"/>
-        <v>9534</v>
+        <v>9537</v>
       </c>
       <c r="U26" s="5">
-        <v>14124</v>
+        <v>14127</v>
       </c>
       <c r="V26" s="4">
         <f t="shared" si="7"/>
-        <v>1.0183863292234481</v>
+        <v>1.0186026389790179</v>
       </c>
       <c r="W26" s="5">
         <v>14474</v>
@@ -4479,14 +4479,14 @@
       </c>
       <c r="Y26" s="3">
         <f t="shared" si="8"/>
-        <v>9577</v>
+        <v>9580</v>
       </c>
       <c r="Z26" s="5">
-        <v>14435</v>
+        <v>14438</v>
       </c>
       <c r="AA26" s="4">
         <f t="shared" si="9"/>
-        <v>0.99730551333425455</v>
+        <v>0.99751278153931189</v>
       </c>
       <c r="AB26" s="5">
         <v>27035</v>
@@ -4496,14 +4496,14 @@
       </c>
       <c r="AD26" s="3">
         <f t="shared" si="10"/>
-        <v>18161</v>
+        <v>18169</v>
       </c>
       <c r="AE26" s="5">
-        <v>27029</v>
+        <v>27037</v>
       </c>
       <c r="AF26" s="4">
         <f t="shared" si="11"/>
-        <v>0.99977806547068615</v>
+        <v>1.0000739781764381</v>
       </c>
       <c r="AG26" s="5">
         <v>14053</v>
@@ -4513,14 +4513,14 @@
       </c>
       <c r="AI26" s="3">
         <f t="shared" si="12"/>
-        <v>9397</v>
+        <v>9402</v>
       </c>
       <c r="AJ26" s="5">
-        <v>14065</v>
+        <v>14070</v>
       </c>
       <c r="AK26" s="4">
         <f t="shared" si="13"/>
-        <v>1.000853910197111</v>
+        <v>1.0012097061125738</v>
       </c>
       <c r="AL26" s="5">
         <v>14372</v>
@@ -4530,14 +4530,14 @@
       </c>
       <c r="AN26" s="3">
         <f>AO26-AM26</f>
-        <v>9122</v>
+        <v>9128</v>
       </c>
       <c r="AO26" s="5">
-        <v>14230</v>
+        <v>14236</v>
       </c>
       <c r="AP26" s="4">
         <f t="shared" si="15"/>
-        <v>0.99011967715001392</v>
+        <v>0.99053715558029498</v>
       </c>
       <c r="AQ26" s="5">
         <v>27267</v>
@@ -4547,14 +4547,14 @@
       </c>
       <c r="AS26" s="3">
         <f>AT26-AR26</f>
-        <v>19139</v>
+        <v>19149</v>
       </c>
       <c r="AT26" s="5">
-        <v>27138</v>
+        <v>27148</v>
       </c>
       <c r="AU26" s="4">
         <f t="shared" si="17"/>
-        <v>0.99526900649136318</v>
+        <v>0.99563575017420325</v>
       </c>
       <c r="AV26" s="5">
         <v>14007</v>
@@ -4564,14 +4564,14 @@
       </c>
       <c r="AX26" s="3">
         <f>AY26-AW26</f>
-        <v>9390</v>
+        <v>9396</v>
       </c>
       <c r="AY26" s="5">
-        <v>13996</v>
+        <v>14002</v>
       </c>
       <c r="AZ26" s="4">
         <f t="shared" si="19"/>
-        <v>0.99921467837509814</v>
+        <v>0.99964303562504464</v>
       </c>
       <c r="BA26" s="5">
         <v>14398</v>
@@ -4581,14 +4581,14 @@
       </c>
       <c r="BC26" s="3">
         <f>BD26-BB26</f>
-        <v>9301</v>
+        <v>9307</v>
       </c>
       <c r="BD26" s="5">
-        <v>14095</v>
+        <v>14101</v>
       </c>
       <c r="BE26" s="4">
         <f t="shared" si="21"/>
-        <v>0.97895541047367685</v>
+        <v>0.97937213501875264</v>
       </c>
       <c r="BF26" s="5">
         <v>27339</v>
@@ -4598,14 +4598,14 @@
       </c>
       <c r="BH26" s="3">
         <f>BI26-BG26</f>
-        <v>19210</v>
+        <v>19222</v>
       </c>
       <c r="BI26" s="5">
-        <v>27163</v>
+        <v>27175</v>
       </c>
       <c r="BJ26" s="4">
         <f t="shared" si="23"/>
-        <v>0.99356231025275243</v>
+        <v>0.99400124364461029</v>
       </c>
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.3">
@@ -4623,14 +4623,14 @@
       </c>
       <c r="E27" s="3">
         <f t="shared" si="0"/>
-        <v>74125</v>
+        <v>74136</v>
       </c>
       <c r="F27" s="5">
-        <v>120716</v>
+        <v>120727</v>
       </c>
       <c r="G27" s="4">
         <f t="shared" si="1"/>
-        <v>1.0019421988346806</v>
+        <v>1.0020334987799007</v>
       </c>
       <c r="H27" s="5">
         <v>123649</v>
@@ -4640,14 +4640,14 @@
       </c>
       <c r="J27" s="3">
         <f t="shared" si="2"/>
-        <v>75158</v>
+        <v>75169</v>
       </c>
       <c r="K27" s="5">
-        <v>122580</v>
+        <v>122591</v>
       </c>
       <c r="L27" s="4">
         <f t="shared" si="3"/>
-        <v>0.99135456008540301</v>
+        <v>0.99144352158125015</v>
       </c>
       <c r="M27" s="5">
         <v>182121</v>
@@ -4657,14 +4657,14 @@
       </c>
       <c r="O27" s="3">
         <f t="shared" si="4"/>
-        <v>115220</v>
+        <v>115232</v>
       </c>
       <c r="P27" s="5">
-        <v>181430</v>
+        <v>181442</v>
       </c>
       <c r="Q27" s="4">
         <f t="shared" si="5"/>
-        <v>0.99620581920810891</v>
+        <v>0.99627170946788124</v>
       </c>
       <c r="R27" s="5">
         <v>122848</v>
@@ -4674,14 +4674,14 @@
       </c>
       <c r="T27" s="3">
         <f t="shared" si="6"/>
-        <v>73663</v>
+        <v>73675</v>
       </c>
       <c r="U27" s="5">
-        <v>121988</v>
+        <v>122000</v>
       </c>
       <c r="V27" s="4">
         <f t="shared" si="7"/>
-        <v>0.99299947903099761</v>
+        <v>0.99309716071893728</v>
       </c>
       <c r="W27" s="5">
         <v>125846</v>
@@ -4691,14 +4691,14 @@
       </c>
       <c r="Y27" s="3">
         <f t="shared" si="8"/>
-        <v>74965</v>
+        <v>74977</v>
       </c>
       <c r="Z27" s="5">
-        <v>123348</v>
+        <v>123360</v>
       </c>
       <c r="AA27" s="4">
         <f t="shared" si="9"/>
-        <v>0.98015034248208133</v>
+        <v>0.98024569712187914</v>
       </c>
       <c r="AB27" s="5">
         <v>184102</v>
@@ -4708,14 +4708,14 @@
       </c>
       <c r="AD27" s="3">
         <f t="shared" si="10"/>
-        <v>113382</v>
+        <v>113398</v>
       </c>
       <c r="AE27" s="5">
-        <v>183192</v>
+        <v>183208</v>
       </c>
       <c r="AF27" s="4">
         <f t="shared" si="11"/>
-        <v>0.99505708791865377</v>
+        <v>0.99514399626294114</v>
       </c>
       <c r="AG27" s="5">
         <v>124176</v>
@@ -4725,14 +4725,14 @@
       </c>
       <c r="AI27" s="3">
         <f t="shared" si="12"/>
-        <v>72911</v>
+        <v>72927</v>
       </c>
       <c r="AJ27" s="5">
-        <v>123174</v>
+        <v>123190</v>
       </c>
       <c r="AK27" s="4">
         <f t="shared" si="13"/>
-        <v>0.99193080788558174</v>
+        <v>0.99205965726066225</v>
       </c>
       <c r="AL27" s="5">
         <v>126536</v>
@@ -4742,14 +4742,14 @@
       </c>
       <c r="AN27" s="3">
         <f t="shared" ref="AN27:AN33" si="24">AO27-AM27</f>
-        <v>74049</v>
+        <v>74064</v>
       </c>
       <c r="AO27" s="5">
-        <v>124113</v>
+        <v>124128</v>
       </c>
       <c r="AP27" s="4">
         <f>AO27/AL27</f>
-        <v>0.98085129923500036</v>
+        <v>0.98096984257444519</v>
       </c>
       <c r="AQ27" s="5">
         <v>184835</v>
@@ -4759,14 +4759,14 @@
       </c>
       <c r="AS27" s="3">
         <f t="shared" ref="AS27:AS33" si="25">AT27-AR27</f>
-        <v>115269</v>
+        <v>115288</v>
       </c>
       <c r="AT27" s="5">
-        <v>184722</v>
+        <v>184741</v>
       </c>
       <c r="AU27" s="4">
         <f>AT27/AQ27</f>
-        <v>0.9993886439256634</v>
+        <v>0.99949143830984388</v>
       </c>
       <c r="AV27" s="5">
         <v>124975</v>
@@ -4776,14 +4776,14 @@
       </c>
       <c r="AX27" s="3">
         <f t="shared" ref="AX27:AX33" si="26">AY27-AW27</f>
-        <v>73651</v>
+        <v>73668</v>
       </c>
       <c r="AY27" s="5">
-        <v>124236</v>
+        <v>124253</v>
       </c>
       <c r="AZ27" s="4">
         <f>AY27/AV27</f>
-        <v>0.99408681736347271</v>
+        <v>0.99422284456891374</v>
       </c>
       <c r="BA27" s="5">
         <v>127493</v>
@@ -4793,14 +4793,14 @@
       </c>
       <c r="BC27" s="3">
         <f t="shared" ref="BC27:BC33" si="27">BD27-BB27</f>
-        <v>74278</v>
+        <v>74299</v>
       </c>
       <c r="BD27" s="5">
-        <v>125372</v>
+        <v>125393</v>
       </c>
       <c r="BE27" s="4">
         <f>BD27/BA27</f>
-        <v>0.98336379252194239</v>
+        <v>0.98352850744746767</v>
       </c>
       <c r="BF27" s="5">
         <v>187636</v>
@@ -4810,14 +4810,14 @@
       </c>
       <c r="BH27" s="3">
         <f t="shared" si="22"/>
-        <v>121636</v>
+        <v>121668</v>
       </c>
       <c r="BI27" s="5">
-        <v>186184</v>
+        <v>186216</v>
       </c>
       <c r="BJ27" s="4">
         <f>BI27/BF27</f>
-        <v>0.99226161291010251</v>
+        <v>0.99243215587627109</v>
       </c>
     </row>
     <row r="28" spans="1:62" x14ac:dyDescent="0.3">
@@ -4869,14 +4869,14 @@
       </c>
       <c r="O28" s="3">
         <f t="shared" si="4"/>
-        <v>302142</v>
+        <v>302144</v>
       </c>
       <c r="P28" s="5">
-        <v>646846</v>
+        <v>646848</v>
       </c>
       <c r="Q28" s="4">
         <f t="shared" si="5"/>
-        <v>0.99378544180208361</v>
+        <v>0.99378851451318273</v>
       </c>
       <c r="R28" s="5">
         <v>389073</v>
@@ -4920,14 +4920,14 @@
       </c>
       <c r="AD28" s="3">
         <f t="shared" si="10"/>
-        <v>292837</v>
+        <v>292840</v>
       </c>
       <c r="AE28" s="5">
-        <v>657475</v>
+        <v>657478</v>
       </c>
       <c r="AF28" s="4">
         <f t="shared" si="11"/>
-        <v>0.99475596157599544</v>
+        <v>0.99476050055905141</v>
       </c>
       <c r="AG28" s="5">
         <v>397417</v>
@@ -4937,14 +4937,14 @@
       </c>
       <c r="AI28" s="3">
         <f t="shared" si="12"/>
-        <v>163432</v>
+        <v>163434</v>
       </c>
       <c r="AJ28" s="5">
-        <v>394445</v>
+        <v>394447</v>
       </c>
       <c r="AK28" s="4">
         <f t="shared" si="13"/>
-        <v>0.99252170893545066</v>
+        <v>0.99252674143280228</v>
       </c>
       <c r="AL28" s="5">
         <v>405895</v>
@@ -4954,14 +4954,14 @@
       </c>
       <c r="AN28" s="3">
         <f t="shared" si="24"/>
-        <v>168534</v>
+        <v>168536</v>
       </c>
       <c r="AO28" s="5">
-        <v>398849</v>
+        <v>398851</v>
       </c>
       <c r="AP28" s="4">
         <f t="shared" ref="AP28:AP33" si="28">AO28/AL28</f>
-        <v>0.98264083075672282</v>
+        <v>0.98264575813942034</v>
       </c>
       <c r="AQ28" s="5">
         <v>670091</v>
@@ -4971,14 +4971,14 @@
       </c>
       <c r="AS28" s="3">
         <f t="shared" si="25"/>
-        <v>296002</v>
+        <v>296013</v>
       </c>
       <c r="AT28" s="5">
-        <v>667130</v>
+        <v>667141</v>
       </c>
       <c r="AU28" s="4">
         <f t="shared" ref="AU28:AU33" si="29">AT28/AQ28</f>
-        <v>0.99558119718068139</v>
+        <v>0.9955976128615367</v>
       </c>
       <c r="AV28" s="5">
         <v>405395</v>
@@ -4988,14 +4988,14 @@
       </c>
       <c r="AX28" s="3">
         <f t="shared" si="26"/>
-        <v>166515</v>
+        <v>166523</v>
       </c>
       <c r="AY28" s="5">
-        <v>402218</v>
+        <v>402226</v>
       </c>
       <c r="AZ28" s="4">
         <f t="shared" ref="AZ28:AZ33" si="30">AY28/AV28</f>
-        <v>0.99216319885543724</v>
+        <v>0.99218293269527247</v>
       </c>
       <c r="BA28" s="5">
         <v>412255</v>
@@ -5005,14 +5005,14 @@
       </c>
       <c r="BC28" s="3">
         <f t="shared" si="27"/>
-        <v>167754</v>
+        <v>167765</v>
       </c>
       <c r="BD28" s="5">
-        <v>406760</v>
+        <v>406771</v>
       </c>
       <c r="BE28" s="4">
         <f t="shared" ref="BE28:BE33" si="31">BD28/BA28</f>
-        <v>0.98667087118409724</v>
+        <v>0.98669755369856038</v>
       </c>
       <c r="BF28" s="5">
         <v>680839</v>
@@ -5022,14 +5022,14 @@
       </c>
       <c r="BH28" s="3">
         <f t="shared" si="22"/>
-        <v>320795</v>
+        <v>320823</v>
       </c>
       <c r="BI28" s="5">
-        <v>677483</v>
+        <v>677511</v>
       </c>
       <c r="BJ28" s="4">
         <f t="shared" si="23"/>
-        <v>0.99507078766051882</v>
+        <v>0.99511191338921534</v>
       </c>
     </row>
     <row r="29" spans="1:62" x14ac:dyDescent="0.3">
@@ -5047,14 +5047,14 @@
       </c>
       <c r="E29" s="3">
         <f t="shared" si="0"/>
-        <v>65994</v>
+        <v>65995</v>
       </c>
       <c r="F29" s="5">
-        <v>126988</v>
+        <v>126989</v>
       </c>
       <c r="G29" s="4">
         <f t="shared" si="1"/>
-        <v>0.99553924912000125</v>
+        <v>0.99554708875247933</v>
       </c>
       <c r="H29" s="5">
         <v>129829</v>
@@ -5064,14 +5064,14 @@
       </c>
       <c r="J29" s="3">
         <f t="shared" si="2"/>
-        <v>67263</v>
+        <v>67265</v>
       </c>
       <c r="K29" s="5">
-        <v>128371</v>
+        <v>128373</v>
       </c>
       <c r="L29" s="4">
         <f t="shared" si="3"/>
-        <v>0.98876984340940777</v>
+        <v>0.98878524828813286</v>
       </c>
       <c r="M29" s="5">
         <v>176637</v>
@@ -5081,14 +5081,14 @@
       </c>
       <c r="O29" s="3">
         <f t="shared" si="4"/>
-        <v>93981</v>
+        <v>93985</v>
       </c>
       <c r="P29" s="5">
-        <v>174574</v>
+        <v>174578</v>
       </c>
       <c r="Q29" s="4">
         <f t="shared" si="5"/>
-        <v>0.98832068026517661</v>
+        <v>0.98834332557731397</v>
       </c>
       <c r="R29" s="5">
         <v>129740</v>
@@ -5098,14 +5098,14 @@
       </c>
       <c r="T29" s="3">
         <f t="shared" si="6"/>
-        <v>67089</v>
+        <v>67092</v>
       </c>
       <c r="U29" s="5">
-        <v>128529</v>
+        <v>128532</v>
       </c>
       <c r="V29" s="4">
         <f t="shared" si="7"/>
-        <v>0.99066594727917379</v>
+        <v>0.99068907044858945</v>
       </c>
       <c r="W29" s="5">
         <v>131766</v>
@@ -5115,14 +5115,14 @@
       </c>
       <c r="Y29" s="3">
         <f t="shared" si="8"/>
-        <v>67110</v>
+        <v>67115</v>
       </c>
       <c r="Z29" s="5">
-        <v>129616</v>
+        <v>129621</v>
       </c>
       <c r="AA29" s="4">
         <f t="shared" si="9"/>
-        <v>0.98368319596861098</v>
+        <v>0.98372114202449801</v>
       </c>
       <c r="AB29" s="5">
         <v>178083</v>
@@ -5132,14 +5132,14 @@
       </c>
       <c r="AD29" s="3">
         <f t="shared" si="10"/>
-        <v>93897</v>
+        <v>93904</v>
       </c>
       <c r="AE29" s="5">
-        <v>176678</v>
+        <v>176685</v>
       </c>
       <c r="AF29" s="4">
         <f t="shared" si="11"/>
-        <v>0.99211042042193809</v>
+        <v>0.9921497279358501</v>
       </c>
       <c r="AG29" s="5">
         <v>131984</v>
@@ -5149,14 +5149,14 @@
       </c>
       <c r="AI29" s="3">
         <f t="shared" si="12"/>
-        <v>68247</v>
+        <v>68251</v>
       </c>
       <c r="AJ29" s="5">
-        <v>130632</v>
+        <v>130636</v>
       </c>
       <c r="AK29" s="4">
         <f t="shared" si="13"/>
-        <v>0.9897563341011032</v>
+        <v>0.98978664080494605</v>
       </c>
       <c r="AL29" s="5">
         <v>133676</v>
@@ -5166,14 +5166,14 @@
       </c>
       <c r="AN29" s="3">
         <f t="shared" si="24"/>
-        <v>68591</v>
+        <v>68596</v>
       </c>
       <c r="AO29" s="5">
-        <v>131861</v>
+        <v>131866</v>
       </c>
       <c r="AP29" s="4">
         <f t="shared" si="28"/>
-        <v>0.98642239444627311</v>
+        <v>0.98645979831832187</v>
       </c>
       <c r="AQ29" s="5">
         <v>179800</v>
@@ -5183,14 +5183,14 @@
       </c>
       <c r="AS29" s="3">
         <f t="shared" si="25"/>
-        <v>93910</v>
+        <v>93918</v>
       </c>
       <c r="AT29" s="5">
-        <v>179275</v>
+        <v>179283</v>
       </c>
       <c r="AU29" s="4">
         <f t="shared" si="29"/>
-        <v>0.99708008898776423</v>
+        <v>0.99712458286985539</v>
       </c>
       <c r="AV29" s="5">
         <v>134089</v>
@@ -5200,14 +5200,14 @@
       </c>
       <c r="AX29" s="3">
         <f t="shared" si="26"/>
-        <v>66911</v>
+        <v>66916</v>
       </c>
       <c r="AY29" s="5">
-        <v>133043</v>
+        <v>133048</v>
       </c>
       <c r="AZ29" s="4">
         <f t="shared" si="30"/>
-        <v>0.99219921097181718</v>
+        <v>0.99223649963829996</v>
       </c>
       <c r="BA29" s="5">
         <v>136058</v>
@@ -5217,14 +5217,14 @@
       </c>
       <c r="BC29" s="3">
         <f t="shared" si="27"/>
-        <v>68612</v>
+        <v>68619</v>
       </c>
       <c r="BD29" s="5">
-        <v>134439</v>
+        <v>134446</v>
       </c>
       <c r="BE29" s="4">
         <f t="shared" si="31"/>
-        <v>0.98810066295256438</v>
+        <v>0.98815211159946492</v>
       </c>
       <c r="BF29" s="5">
         <v>182623</v>
@@ -5234,14 +5234,14 @@
       </c>
       <c r="BH29" s="3">
         <f t="shared" si="22"/>
-        <v>100492</v>
+        <v>100505</v>
       </c>
       <c r="BI29" s="5">
-        <v>181767</v>
+        <v>181780</v>
       </c>
       <c r="BJ29" s="4">
         <f t="shared" si="23"/>
-        <v>0.9953127481204449</v>
+        <v>0.99538393302048478</v>
       </c>
     </row>
     <row r="30" spans="1:62" x14ac:dyDescent="0.3">
@@ -5344,14 +5344,14 @@
       </c>
       <c r="AD30" s="3">
         <f t="shared" si="10"/>
-        <v>173241</v>
+        <v>173242</v>
       </c>
       <c r="AE30" s="5">
-        <v>291166</v>
+        <v>291167</v>
       </c>
       <c r="AF30" s="4">
         <f t="shared" si="11"/>
-        <v>0.99270048106591391</v>
+        <v>0.99270389046289387</v>
       </c>
       <c r="AG30" s="5">
         <v>172053</v>
@@ -5378,14 +5378,14 @@
       </c>
       <c r="AN30" s="3">
         <f t="shared" si="24"/>
-        <v>96575</v>
+        <v>96576</v>
       </c>
       <c r="AO30" s="5">
-        <v>173523</v>
+        <v>173524</v>
       </c>
       <c r="AP30" s="4">
         <f t="shared" si="28"/>
-        <v>0.98127067605394858</v>
+        <v>0.98127633104306278</v>
       </c>
       <c r="AQ30" s="5">
         <v>297651</v>
@@ -5395,14 +5395,14 @@
       </c>
       <c r="AS30" s="3">
         <f t="shared" si="25"/>
-        <v>175622</v>
+        <v>175629</v>
       </c>
       <c r="AT30" s="5">
-        <v>296838</v>
+        <v>296845</v>
       </c>
       <c r="AU30" s="4">
         <f t="shared" si="29"/>
-        <v>0.99726861324168237</v>
+        <v>0.99729213071684619</v>
       </c>
       <c r="AV30" s="5">
         <v>175428</v>
@@ -5412,14 +5412,14 @@
       </c>
       <c r="AX30" s="3">
         <f t="shared" si="26"/>
-        <v>96853</v>
+        <v>96857</v>
       </c>
       <c r="AY30" s="5">
-        <v>174088</v>
+        <v>174092</v>
       </c>
       <c r="AZ30" s="4">
         <f t="shared" si="30"/>
-        <v>0.99236153863693366</v>
+        <v>0.99238434001413689</v>
       </c>
       <c r="BA30" s="5">
         <v>179593</v>
@@ -5429,14 +5429,14 @@
       </c>
       <c r="BC30" s="3">
         <f t="shared" si="27"/>
-        <v>98807</v>
+        <v>98812</v>
       </c>
       <c r="BD30" s="5">
-        <v>176069</v>
+        <v>176074</v>
       </c>
       <c r="BE30" s="4">
         <f t="shared" si="31"/>
-        <v>0.98037785437071601</v>
+        <v>0.98040569509947495</v>
       </c>
       <c r="BF30" s="5">
         <v>302258</v>
@@ -5446,14 +5446,14 @@
       </c>
       <c r="BH30" s="3">
         <f t="shared" si="22"/>
-        <v>185101</v>
+        <v>185116</v>
       </c>
       <c r="BI30" s="5">
-        <v>300134</v>
+        <v>300149</v>
       </c>
       <c r="BJ30" s="4">
         <f t="shared" si="23"/>
-        <v>0.99297289070926165</v>
+        <v>0.99302251718730361</v>
       </c>
     </row>
     <row r="31" spans="1:62" x14ac:dyDescent="0.3">
@@ -5471,14 +5471,14 @@
       </c>
       <c r="E31" s="3">
         <f t="shared" si="0"/>
-        <v>35554</v>
+        <v>35556</v>
       </c>
       <c r="F31" s="5">
-        <v>74334</v>
+        <v>74336</v>
       </c>
       <c r="G31" s="4">
         <f t="shared" si="1"/>
-        <v>0.99763790095289218</v>
+        <v>0.9976647429875185</v>
       </c>
       <c r="H31" s="5">
         <v>76671</v>
@@ -5488,14 +5488,14 @@
       </c>
       <c r="J31" s="3">
         <f t="shared" si="2"/>
-        <v>35330</v>
+        <v>35332</v>
       </c>
       <c r="K31" s="5">
-        <v>75514</v>
+        <v>75516</v>
       </c>
       <c r="L31" s="4">
         <f t="shared" si="3"/>
-        <v>0.98490954859073188</v>
+        <v>0.98493563407285678</v>
       </c>
       <c r="M31" s="5">
         <v>133745</v>
@@ -5505,14 +5505,14 @@
       </c>
       <c r="O31" s="3">
         <f t="shared" si="4"/>
-        <v>70019</v>
+        <v>70021</v>
       </c>
       <c r="P31" s="5">
-        <v>133853</v>
+        <v>133855</v>
       </c>
       <c r="Q31" s="4">
         <f t="shared" si="5"/>
-        <v>1.0008075068226849</v>
+        <v>1.0008224606527347</v>
       </c>
       <c r="R31" s="5">
         <v>74974</v>
@@ -5522,14 +5522,14 @@
       </c>
       <c r="T31" s="3">
         <f t="shared" si="6"/>
-        <v>34163</v>
+        <v>34165</v>
       </c>
       <c r="U31" s="5">
-        <v>74782</v>
+        <v>74784</v>
       </c>
       <c r="V31" s="4">
         <f t="shared" si="7"/>
-        <v>0.99743911222557158</v>
+        <v>0.99746578813988851</v>
       </c>
       <c r="W31" s="5">
         <v>77586</v>
@@ -5539,14 +5539,14 @@
       </c>
       <c r="Y31" s="3">
         <f t="shared" si="8"/>
-        <v>34639</v>
+        <v>34641</v>
       </c>
       <c r="Z31" s="5">
-        <v>75897</v>
+        <v>75899</v>
       </c>
       <c r="AA31" s="4">
         <f t="shared" si="9"/>
-        <v>0.97823060861495625</v>
+        <v>0.97825638646147506</v>
       </c>
       <c r="AB31" s="5">
         <v>135116</v>
@@ -5556,14 +5556,14 @@
       </c>
       <c r="AD31" s="3">
         <f t="shared" si="10"/>
-        <v>70316</v>
+        <v>70318</v>
       </c>
       <c r="AE31" s="5">
-        <v>135429</v>
+        <v>135431</v>
       </c>
       <c r="AF31" s="4">
         <f t="shared" si="11"/>
-        <v>1.0023165280203676</v>
+        <v>1.0023313301163446</v>
       </c>
       <c r="AG31" s="5">
         <v>76230</v>
@@ -5573,14 +5573,14 @@
       </c>
       <c r="AI31" s="3">
         <f t="shared" si="12"/>
-        <v>33312</v>
+        <v>33314</v>
       </c>
       <c r="AJ31" s="5">
-        <v>75677</v>
+        <v>75679</v>
       </c>
       <c r="AK31" s="4">
         <f t="shared" si="13"/>
-        <v>0.99274563820018369</v>
+        <v>0.99277187459005645</v>
       </c>
       <c r="AL31" s="5">
         <v>77611</v>
@@ -5590,14 +5590,14 @@
       </c>
       <c r="AN31" s="3">
         <f t="shared" si="24"/>
-        <v>33395</v>
+        <v>33397</v>
       </c>
       <c r="AO31" s="5">
-        <v>76717</v>
+        <v>76719</v>
       </c>
       <c r="AP31" s="4">
         <f t="shared" si="28"/>
-        <v>0.98848101428921153</v>
+        <v>0.98850678383218871</v>
       </c>
       <c r="AQ31" s="5">
         <v>136879</v>
@@ -5607,14 +5607,14 @@
       </c>
       <c r="AS31" s="3">
         <f t="shared" si="25"/>
-        <v>69319</v>
+        <v>69321</v>
       </c>
       <c r="AT31" s="5">
-        <v>137681</v>
+        <v>137683</v>
       </c>
       <c r="AU31" s="4">
         <f t="shared" si="29"/>
-        <v>1.0058591895031379</v>
+        <v>1.0058738009482828</v>
       </c>
       <c r="AV31" s="5">
         <v>76719</v>
@@ -5624,14 +5624,14 @@
       </c>
       <c r="AX31" s="3">
         <f t="shared" si="26"/>
-        <v>33136</v>
+        <v>33137</v>
       </c>
       <c r="AY31" s="5">
-        <v>76699</v>
+        <v>76700</v>
       </c>
       <c r="AZ31" s="4">
         <f t="shared" si="30"/>
-        <v>0.9997393083851458</v>
+        <v>0.99975234296588855</v>
       </c>
       <c r="BA31" s="5">
         <v>78720</v>
@@ -5641,14 +5641,14 @@
       </c>
       <c r="BC31" s="3">
         <f t="shared" si="27"/>
-        <v>33796</v>
+        <v>33798</v>
       </c>
       <c r="BD31" s="5">
-        <v>78209</v>
+        <v>78211</v>
       </c>
       <c r="BE31" s="4">
         <f t="shared" si="31"/>
-        <v>0.99350863821138213</v>
+        <v>0.99353404471544715</v>
       </c>
       <c r="BF31" s="5">
         <v>140181</v>
@@ -5658,14 +5658,14 @@
       </c>
       <c r="BH31" s="3">
         <f t="shared" si="22"/>
-        <v>76266</v>
+        <v>76269</v>
       </c>
       <c r="BI31" s="5">
-        <v>140499</v>
+        <v>140502</v>
       </c>
       <c r="BJ31" s="4">
         <f t="shared" si="23"/>
-        <v>1.0022684957305199</v>
+        <v>1.002289896633638</v>
       </c>
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.3">
@@ -5683,14 +5683,14 @@
       </c>
       <c r="E32" s="3">
         <f t="shared" si="0"/>
-        <v>93783</v>
+        <v>93785</v>
       </c>
       <c r="F32" s="5">
-        <v>202835</v>
+        <v>202837</v>
       </c>
       <c r="G32" s="4">
         <f t="shared" si="1"/>
-        <v>0.99566557692496493</v>
+        <v>0.99567539441777364</v>
       </c>
       <c r="H32" s="5">
         <v>210874</v>
@@ -5700,14 +5700,14 @@
       </c>
       <c r="J32" s="3">
         <f t="shared" si="2"/>
-        <v>94717</v>
+        <v>94719</v>
       </c>
       <c r="K32" s="5">
-        <v>207286</v>
+        <v>207288</v>
       </c>
       <c r="L32" s="4">
         <f t="shared" si="3"/>
-        <v>0.98298510010717299</v>
+        <v>0.98299458444379106</v>
       </c>
       <c r="M32" s="5">
         <v>441035</v>
@@ -5717,14 +5717,14 @@
       </c>
       <c r="O32" s="3">
         <f t="shared" si="4"/>
-        <v>233999</v>
+        <v>234002</v>
       </c>
       <c r="P32" s="5">
-        <v>439433</v>
+        <v>439436</v>
       </c>
       <c r="Q32" s="4">
         <f t="shared" si="5"/>
-        <v>0.99636763522169447</v>
+        <v>0.99637443740292719</v>
       </c>
       <c r="R32" s="5">
         <v>206418</v>
@@ -5734,14 +5734,14 @@
       </c>
       <c r="T32" s="3">
         <f t="shared" si="6"/>
-        <v>92303</v>
+        <v>92305</v>
       </c>
       <c r="U32" s="5">
-        <v>204379</v>
+        <v>204381</v>
       </c>
       <c r="V32" s="4">
         <f t="shared" si="7"/>
-        <v>0.99012198548576191</v>
+        <v>0.99013167456326479</v>
       </c>
       <c r="W32" s="5">
         <v>212709</v>
@@ -5751,14 +5751,14 @@
       </c>
       <c r="Y32" s="3">
         <f t="shared" si="8"/>
-        <v>95927</v>
+        <v>95929</v>
       </c>
       <c r="Z32" s="5">
-        <v>208796</v>
+        <v>208798</v>
       </c>
       <c r="AA32" s="4">
         <f t="shared" si="9"/>
-        <v>0.9816039753842104</v>
+        <v>0.98161337790126413</v>
       </c>
       <c r="AB32" s="5">
         <v>446806</v>
@@ -5768,14 +5768,14 @@
       </c>
       <c r="AD32" s="3">
         <f t="shared" si="10"/>
-        <v>237852</v>
+        <v>237856</v>
       </c>
       <c r="AE32" s="5">
-        <v>445880</v>
+        <v>445884</v>
       </c>
       <c r="AF32" s="4">
         <f t="shared" si="11"/>
-        <v>0.99792751216411602</v>
+        <v>0.99793646459537244</v>
       </c>
       <c r="AG32" s="5">
         <v>210129</v>
@@ -5785,14 +5785,14 @@
       </c>
       <c r="AI32" s="3">
         <f t="shared" si="12"/>
-        <v>92556</v>
+        <v>92557</v>
       </c>
       <c r="AJ32" s="5">
-        <v>208782</v>
+        <v>208783</v>
       </c>
       <c r="AK32" s="4">
         <f t="shared" si="13"/>
-        <v>0.9935896520708708</v>
+        <v>0.99359441105225832</v>
       </c>
       <c r="AL32" s="5">
         <v>217332</v>
@@ -5802,14 +5802,14 @@
       </c>
       <c r="AN32" s="3">
         <f t="shared" si="24"/>
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="AO32" s="5">
-        <v>212392</v>
+        <v>212394</v>
       </c>
       <c r="AP32" s="4">
         <f t="shared" si="28"/>
-        <v>0.97726979920122214</v>
+        <v>0.97727900171166693</v>
       </c>
       <c r="AQ32" s="5">
         <v>453805</v>
@@ -5819,14 +5819,14 @@
       </c>
       <c r="AS32" s="3">
         <f t="shared" si="25"/>
-        <v>229544</v>
+        <v>229553</v>
       </c>
       <c r="AT32" s="5">
-        <v>453658</v>
+        <v>453667</v>
       </c>
       <c r="AU32" s="4">
         <f t="shared" si="29"/>
-        <v>0.99967607232181221</v>
+        <v>0.99969590462864011</v>
       </c>
       <c r="AV32" s="5">
         <v>213428</v>
@@ -5836,14 +5836,14 @@
       </c>
       <c r="AX32" s="3">
         <f t="shared" si="26"/>
-        <v>91571</v>
+        <v>91575</v>
       </c>
       <c r="AY32" s="5">
-        <v>212598</v>
+        <v>212602</v>
       </c>
       <c r="AZ32" s="4">
         <f t="shared" si="30"/>
-        <v>0.99611110069906483</v>
+        <v>0.99612984238244284</v>
       </c>
       <c r="BA32" s="5">
         <v>220509</v>
@@ -5853,14 +5853,14 @@
       </c>
       <c r="BC32" s="3">
         <f t="shared" si="27"/>
-        <v>94380</v>
+        <v>94382</v>
       </c>
       <c r="BD32" s="5">
-        <v>217110</v>
+        <v>217112</v>
       </c>
       <c r="BE32" s="4">
         <f t="shared" si="31"/>
-        <v>0.98458566317021079</v>
+        <v>0.98459473309479428</v>
       </c>
       <c r="BF32" s="5">
         <v>463937</v>
@@ -5870,14 +5870,14 @@
       </c>
       <c r="BH32" s="3">
         <f t="shared" si="22"/>
-        <v>253955</v>
+        <v>253964</v>
       </c>
       <c r="BI32" s="5">
-        <v>461929</v>
+        <v>461938</v>
       </c>
       <c r="BJ32" s="4">
         <f t="shared" si="23"/>
-        <v>0.99567182613156524</v>
+        <v>0.99569122531723053</v>
       </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.3">
@@ -5895,14 +5895,14 @@
       </c>
       <c r="E33" s="3">
         <f t="shared" si="0"/>
-        <v>96269</v>
+        <v>96271</v>
       </c>
       <c r="F33" s="5">
-        <v>620528</v>
+        <v>620530</v>
       </c>
       <c r="G33" s="4">
         <f t="shared" si="1"/>
-        <v>0.99924798106264945</v>
+        <v>0.99925120170049675</v>
       </c>
       <c r="H33" s="5">
         <v>630476</v>
@@ -5912,14 +5912,14 @@
       </c>
       <c r="J33" s="3">
         <f t="shared" si="2"/>
-        <v>98480</v>
+        <v>98482</v>
       </c>
       <c r="K33" s="5">
-        <v>628337</v>
+        <v>628339</v>
       </c>
       <c r="L33" s="4">
         <f t="shared" si="3"/>
-        <v>0.99660732525901063</v>
+        <v>0.99661049746540709</v>
       </c>
       <c r="M33" s="5">
         <v>1032030</v>
@@ -5929,14 +5929,14 @@
       </c>
       <c r="O33" s="3">
         <f t="shared" si="4"/>
-        <v>184054</v>
+        <v>184057</v>
       </c>
       <c r="P33" s="5">
-        <v>1033754</v>
+        <v>1033757</v>
       </c>
       <c r="Q33" s="4">
         <f t="shared" si="5"/>
-        <v>1.0016704940747847</v>
+        <v>1.0016734009670261</v>
       </c>
       <c r="R33" s="5">
         <v>629419</v>
@@ -5946,14 +5946,14 @@
       </c>
       <c r="T33" s="3">
         <f t="shared" si="6"/>
-        <v>97175</v>
+        <v>97177</v>
       </c>
       <c r="U33" s="5">
-        <v>627901</v>
+        <v>627903</v>
       </c>
       <c r="V33" s="4">
         <f t="shared" si="7"/>
-        <v>0.99758825202289736</v>
+        <v>0.99759142955646396</v>
       </c>
       <c r="W33" s="5">
         <v>637378</v>
@@ -5963,14 +5963,14 @@
       </c>
       <c r="Y33" s="3">
         <f t="shared" si="8"/>
-        <v>101398</v>
+        <v>101399</v>
       </c>
       <c r="Z33" s="5">
-        <v>634258</v>
+        <v>634259</v>
       </c>
       <c r="AA33" s="4">
         <f t="shared" si="9"/>
-        <v>0.99510494557389806</v>
+        <v>0.9951065145015987</v>
       </c>
       <c r="AB33" s="5">
         <v>1041984</v>
@@ -5980,14 +5980,14 @@
       </c>
       <c r="AD33" s="3">
         <f t="shared" si="10"/>
-        <v>184414</v>
+        <v>184417</v>
       </c>
       <c r="AE33" s="5">
-        <v>1043593</v>
+        <v>1043596</v>
       </c>
       <c r="AF33" s="4">
         <f t="shared" si="11"/>
-        <v>1.0015441695841778</v>
+        <v>1.0015470487070819</v>
       </c>
       <c r="AG33" s="5">
         <v>638215</v>
@@ -6031,14 +6031,14 @@
       </c>
       <c r="AS33" s="3">
         <f t="shared" si="25"/>
-        <v>167729</v>
+        <v>167731</v>
       </c>
       <c r="AT33" s="5">
-        <v>1055185</v>
+        <v>1055187</v>
       </c>
       <c r="AU33" s="4">
         <f t="shared" si="29"/>
-        <v>1.0019484718454363</v>
+        <v>1.0019503709408024</v>
       </c>
       <c r="AV33" s="5">
         <v>647979</v>
@@ -6048,14 +6048,14 @@
       </c>
       <c r="AX33" s="3">
         <f t="shared" si="26"/>
-        <v>89183</v>
+        <v>89184</v>
       </c>
       <c r="AY33" s="5">
-        <v>647886</v>
+        <v>647887</v>
       </c>
       <c r="AZ33" s="4">
         <f t="shared" si="30"/>
-        <v>0.99985647683026768</v>
+        <v>0.99985802009015723</v>
       </c>
       <c r="BA33" s="5">
         <v>657743</v>
@@ -6065,14 +6065,14 @@
       </c>
       <c r="BC33" s="3">
         <f t="shared" si="27"/>
-        <v>89586</v>
+        <v>89588</v>
       </c>
       <c r="BD33" s="5">
-        <v>657191</v>
+        <v>657193</v>
       </c>
       <c r="BE33" s="4">
         <f t="shared" si="31"/>
-        <v>0.99916076643917151</v>
+        <v>0.99916380714047892</v>
       </c>
       <c r="BF33" s="5">
         <v>1071541</v>
@@ -6082,14 +6082,14 @@
       </c>
       <c r="BH33" s="3">
         <f t="shared" si="22"/>
-        <v>189781</v>
+        <v>189783</v>
       </c>
       <c r="BI33" s="5">
-        <v>1072577</v>
+        <v>1072579</v>
       </c>
       <c r="BJ33" s="4">
         <f t="shared" si="23"/>
-        <v>1.0009668318804414</v>
+        <v>1.0009686983512529</v>
       </c>
     </row>
     <row r="34" spans="1:62" x14ac:dyDescent="0.3">
@@ -6507,14 +6507,14 @@
       </c>
       <c r="E36" s="3">
         <f t="shared" si="0"/>
-        <v>253998</v>
+        <v>254003</v>
       </c>
       <c r="F36" s="5">
-        <v>833197</v>
+        <v>833202</v>
       </c>
       <c r="G36" s="4">
         <f t="shared" si="1"/>
-        <v>0.99660302115815447</v>
+        <v>0.99660900175470701</v>
       </c>
       <c r="H36" s="5">
         <v>854298</v>
@@ -6524,14 +6524,14 @@
       </c>
       <c r="J36" s="3">
         <f t="shared" si="32"/>
-        <v>261271</v>
+        <v>261280</v>
       </c>
       <c r="K36" s="5">
-        <v>843361</v>
+        <v>843370</v>
       </c>
       <c r="L36" s="4">
         <f t="shared" si="33"/>
-        <v>0.98719767575248918</v>
+        <v>0.98720821071803988</v>
       </c>
       <c r="M36" s="5">
         <v>1510524</v>
@@ -6541,14 +6541,14 @@
       </c>
       <c r="O36" s="3">
         <f t="shared" si="34"/>
-        <v>489861</v>
+        <v>489869</v>
       </c>
       <c r="P36" s="5">
-        <v>1504252</v>
+        <v>1504260</v>
       </c>
       <c r="Q36" s="4">
         <f t="shared" si="35"/>
-        <v>0.99584779851230432</v>
+        <v>0.99585309468767125</v>
       </c>
       <c r="R36" s="5">
         <v>845008</v>
@@ -6558,14 +6558,14 @@
       </c>
       <c r="T36" s="3">
         <f t="shared" si="36"/>
-        <v>248838</v>
+        <v>248847</v>
       </c>
       <c r="U36" s="5">
-        <v>839804</v>
+        <v>839813</v>
       </c>
       <c r="V36" s="4">
         <f t="shared" si="37"/>
-        <v>0.99384147842387294</v>
+        <v>0.99385212921061106</v>
       </c>
       <c r="W36" s="5">
         <v>865288</v>
@@ -6575,14 +6575,14 @@
       </c>
       <c r="Y36" s="3">
         <f t="shared" si="38"/>
-        <v>251391</v>
+        <v>251399</v>
       </c>
       <c r="Z36" s="5">
-        <v>849476</v>
+        <v>849484</v>
       </c>
       <c r="AA36" s="4">
         <f t="shared" si="39"/>
-        <v>0.98172631540019051</v>
+        <v>0.981735560876841</v>
       </c>
       <c r="AB36" s="5">
         <v>1522408</v>
@@ -6592,14 +6592,14 @@
       </c>
       <c r="AD36" s="3">
         <f t="shared" si="40"/>
-        <v>486006</v>
+        <v>486016</v>
       </c>
       <c r="AE36" s="5">
-        <v>1517976</v>
+        <v>1517986</v>
       </c>
       <c r="AF36" s="4">
         <f t="shared" si="41"/>
-        <v>0.9970888224444433</v>
+        <v>0.9970953909858592</v>
       </c>
       <c r="AG36" s="5">
         <v>860909</v>
@@ -6609,14 +6609,14 @@
       </c>
       <c r="AI36" s="3">
         <f t="shared" si="42"/>
-        <v>232935</v>
+        <v>232946</v>
       </c>
       <c r="AJ36" s="5">
-        <v>855828</v>
+        <v>855839</v>
       </c>
       <c r="AK36" s="4">
         <f t="shared" si="43"/>
-        <v>0.99409809863760279</v>
+        <v>0.99411087583008195</v>
       </c>
       <c r="AL36" s="5">
         <v>879793</v>
@@ -6626,14 +6626,14 @@
       </c>
       <c r="AN36" s="3">
         <f t="shared" si="44"/>
-        <v>238578</v>
+        <v>238589</v>
       </c>
       <c r="AO36" s="5">
-        <v>866318</v>
+        <v>866329</v>
       </c>
       <c r="AP36" s="4">
         <f t="shared" si="45"/>
-        <v>0.98468389723491778</v>
+        <v>0.9846964001759505</v>
       </c>
       <c r="AQ36" s="5">
         <v>1539776</v>
@@ -6643,14 +6643,14 @@
       </c>
       <c r="AS36" s="3">
         <f t="shared" si="46"/>
-        <v>458721</v>
+        <v>458740</v>
       </c>
       <c r="AT36" s="5">
-        <v>1539497</v>
+        <v>1539516</v>
       </c>
       <c r="AU36" s="4">
         <f t="shared" si="47"/>
-        <v>0.99981880481316765</v>
+        <v>0.99983114427033537</v>
       </c>
       <c r="AV36" s="5">
         <v>875330</v>
@@ -6660,14 +6660,14 @@
       </c>
       <c r="AX36" s="3">
         <f t="shared" si="48"/>
-        <v>234345</v>
+        <v>234356</v>
       </c>
       <c r="AY36" s="5">
-        <v>872496</v>
+        <v>872507</v>
       </c>
       <c r="AZ36" s="4">
         <f t="shared" si="49"/>
-        <v>0.99676236390846884</v>
+        <v>0.99677493059760314</v>
       </c>
       <c r="BA36" s="5">
         <v>893595</v>
@@ -6677,14 +6677,14 @@
       </c>
       <c r="BC36" s="3">
         <f t="shared" si="50"/>
-        <v>236004</v>
+        <v>236022</v>
       </c>
       <c r="BD36" s="5">
-        <v>883734</v>
+        <v>883752</v>
       </c>
       <c r="BE36" s="4">
         <f t="shared" si="51"/>
-        <v>0.98896479948970173</v>
+        <v>0.98898494284323435</v>
       </c>
       <c r="BF36" s="5">
         <v>1566403</v>
@@ -6694,14 +6694,14 @@
       </c>
       <c r="BH36" s="3">
         <f t="shared" si="52"/>
-        <v>507359</v>
+        <v>507383</v>
       </c>
       <c r="BI36" s="5">
-        <v>1560430</v>
+        <v>1560454</v>
       </c>
       <c r="BJ36" s="4">
         <f t="shared" si="53"/>
-        <v>0.99618680505591473</v>
+        <v>0.99620212678346509</v>
       </c>
     </row>
     <row r="37" spans="1:62" x14ac:dyDescent="0.3">
@@ -6719,14 +6719,14 @@
       </c>
       <c r="E37" s="3">
         <f t="shared" si="0"/>
-        <v>283686</v>
+        <v>283690</v>
       </c>
       <c r="F37" s="5">
-        <v>667695</v>
+        <v>667699</v>
       </c>
       <c r="G37" s="4">
         <f t="shared" si="1"/>
-        <v>0.98837390033883554</v>
+        <v>0.98837982144892522</v>
       </c>
       <c r="H37" s="5">
         <v>681828</v>
@@ -6736,14 +6736,14 @@
       </c>
       <c r="J37" s="3">
         <f t="shared" si="32"/>
-        <v>274164</v>
+        <v>274167</v>
       </c>
       <c r="K37" s="5">
-        <v>670565</v>
+        <v>670568</v>
       </c>
       <c r="L37" s="4">
         <f t="shared" si="33"/>
-        <v>0.98348117120446799</v>
+        <v>0.98348557114110891</v>
       </c>
       <c r="M37" s="5">
         <v>856106</v>
@@ -6753,14 +6753,14 @@
       </c>
       <c r="O37" s="3">
         <f t="shared" si="34"/>
-        <v>347702</v>
+        <v>347706</v>
       </c>
       <c r="P37" s="5">
-        <v>846338</v>
+        <v>846342</v>
       </c>
       <c r="Q37" s="4">
         <f t="shared" si="35"/>
-        <v>0.98859019794277814</v>
+        <v>0.98859487026139281</v>
       </c>
       <c r="R37" s="5">
         <v>679636</v>
@@ -6770,14 +6770,14 @@
       </c>
       <c r="T37" s="3">
         <f t="shared" si="36"/>
-        <v>268955</v>
+        <v>268959</v>
       </c>
       <c r="U37" s="5">
-        <v>671504</v>
+        <v>671508</v>
       </c>
       <c r="V37" s="4">
         <f t="shared" si="37"/>
-        <v>0.98803477155418484</v>
+        <v>0.98804065705760147</v>
       </c>
       <c r="W37" s="5">
         <v>687189</v>
@@ -6787,14 +6787,14 @@
       </c>
       <c r="Y37" s="3">
         <f t="shared" si="38"/>
-        <v>273295</v>
+        <v>273301</v>
       </c>
       <c r="Z37" s="5">
-        <v>676610</v>
+        <v>676616</v>
       </c>
       <c r="AA37" s="4">
         <f t="shared" si="39"/>
-        <v>0.98460539967898209</v>
+        <v>0.98461413090139682</v>
       </c>
       <c r="AB37" s="5">
         <v>863912</v>
@@ -6804,14 +6804,14 @@
       </c>
       <c r="AD37" s="3">
         <f t="shared" si="40"/>
-        <v>349285</v>
+        <v>349295</v>
       </c>
       <c r="AE37" s="5">
-        <v>855456</v>
+        <v>855466</v>
       </c>
       <c r="AF37" s="4">
         <f t="shared" si="41"/>
-        <v>0.99021196603357753</v>
+        <v>0.9902235412866125</v>
       </c>
       <c r="AG37" s="5">
         <v>690763</v>
@@ -6821,14 +6821,14 @@
       </c>
       <c r="AI37" s="3">
         <f t="shared" si="42"/>
-        <v>260657</v>
+        <v>260665</v>
       </c>
       <c r="AJ37" s="5">
-        <v>682637</v>
+        <v>682645</v>
       </c>
       <c r="AK37" s="4">
         <f t="shared" si="43"/>
-        <v>0.98823619678529395</v>
+        <v>0.9882477781815181</v>
       </c>
       <c r="AL37" s="5">
         <v>697437</v>
@@ -6838,14 +6838,14 @@
       </c>
       <c r="AN37" s="3">
         <f t="shared" si="44"/>
-        <v>265012</v>
+        <v>265022</v>
       </c>
       <c r="AO37" s="5">
-        <v>688628</v>
+        <v>688638</v>
       </c>
       <c r="AP37" s="4">
         <f t="shared" si="45"/>
-        <v>0.98736946849679608</v>
+        <v>0.98738380670942316</v>
       </c>
       <c r="AQ37" s="5">
         <v>873380</v>
@@ -6855,14 +6855,14 @@
       </c>
       <c r="AS37" s="3">
         <f t="shared" si="46"/>
-        <v>338570</v>
+        <v>338585</v>
       </c>
       <c r="AT37" s="5">
-        <v>868980</v>
+        <v>868995</v>
       </c>
       <c r="AU37" s="4">
         <f t="shared" si="47"/>
-        <v>0.99496210126176465</v>
+        <v>0.99497927591655411</v>
       </c>
       <c r="AV37" s="5">
         <v>700086</v>
@@ -6872,14 +6872,14 @@
       </c>
       <c r="AX37" s="3">
         <f t="shared" si="48"/>
-        <v>266975</v>
+        <v>266992</v>
       </c>
       <c r="AY37" s="5">
-        <v>694488</v>
+        <v>694505</v>
       </c>
       <c r="AZ37" s="4">
         <f t="shared" si="49"/>
-        <v>0.99200383952828652</v>
+        <v>0.99202812225926529</v>
       </c>
       <c r="BA37" s="5">
         <v>708485</v>
@@ -6889,14 +6889,14 @@
       </c>
       <c r="BC37" s="3">
         <f t="shared" si="50"/>
-        <v>268870</v>
+        <v>268885</v>
       </c>
       <c r="BD37" s="5">
-        <v>699470</v>
+        <v>699485</v>
       </c>
       <c r="BE37" s="4">
         <f t="shared" si="51"/>
-        <v>0.98727566568099534</v>
+        <v>0.98729683761829823</v>
       </c>
       <c r="BF37" s="5">
         <v>887779</v>
@@ -6906,14 +6906,14 @@
       </c>
       <c r="BH37" s="3">
         <f t="shared" si="52"/>
-        <v>384188</v>
+        <v>384214</v>
       </c>
       <c r="BI37" s="5">
-        <v>878249</v>
+        <v>878275</v>
       </c>
       <c r="BJ37" s="4">
         <f t="shared" si="53"/>
-        <v>0.98926534644320263</v>
+        <v>0.98929463301114351</v>
       </c>
     </row>
     <row r="38" spans="1:62" x14ac:dyDescent="0.3">
@@ -6931,14 +6931,14 @@
       </c>
       <c r="E38" s="3">
         <f t="shared" si="0"/>
-        <v>9415</v>
+        <v>9416</v>
       </c>
       <c r="F38" s="5">
-        <v>22899</v>
+        <v>22900</v>
       </c>
       <c r="G38" s="4">
         <f t="shared" si="1"/>
-        <v>1.007124950521177</v>
+        <v>1.0071689316972336</v>
       </c>
       <c r="H38" s="5">
         <v>23122</v>
@@ -6948,14 +6948,14 @@
       </c>
       <c r="J38" s="3">
         <f t="shared" si="32"/>
-        <v>9602</v>
+        <v>9603</v>
       </c>
       <c r="K38" s="5">
-        <v>23172</v>
+        <v>23173</v>
       </c>
       <c r="L38" s="4">
         <f t="shared" si="33"/>
-        <v>1.0021624426952687</v>
+        <v>1.0022056915491739</v>
       </c>
       <c r="M38" s="5">
         <v>35582</v>
@@ -6965,14 +6965,14 @@
       </c>
       <c r="O38" s="3">
         <f t="shared" si="34"/>
-        <v>14389</v>
+        <v>14390</v>
       </c>
       <c r="P38" s="5">
-        <v>35830</v>
+        <v>35831</v>
       </c>
       <c r="Q38" s="4">
         <f t="shared" si="35"/>
-        <v>1.0069698161992018</v>
+        <v>1.0069979202967794</v>
       </c>
       <c r="R38" s="5">
         <v>22911</v>
@@ -6982,14 +6982,14 @@
       </c>
       <c r="T38" s="3">
         <f t="shared" si="36"/>
-        <v>9354</v>
+        <v>9355</v>
       </c>
       <c r="U38" s="5">
-        <v>23143</v>
+        <v>23144</v>
       </c>
       <c r="V38" s="4">
         <f t="shared" si="37"/>
-        <v>1.0101261402819606</v>
+        <v>1.0101697874383484</v>
       </c>
       <c r="W38" s="5">
         <v>23450</v>
@@ -6999,14 +6999,14 @@
       </c>
       <c r="Y38" s="3">
         <f t="shared" si="38"/>
-        <v>9183</v>
+        <v>9184</v>
       </c>
       <c r="Z38" s="5">
-        <v>23351</v>
+        <v>23352</v>
       </c>
       <c r="AA38" s="4">
         <f t="shared" si="39"/>
-        <v>0.99577825159914712</v>
+        <v>0.99582089552238806</v>
       </c>
       <c r="AB38" s="5">
         <v>35915</v>
@@ -7016,14 +7016,14 @@
       </c>
       <c r="AD38" s="3">
         <f t="shared" si="40"/>
-        <v>14261</v>
+        <v>14262</v>
       </c>
       <c r="AE38" s="5">
-        <v>36328</v>
+        <v>36329</v>
       </c>
       <c r="AF38" s="4">
         <f t="shared" si="41"/>
-        <v>1.0114993735208131</v>
+        <v>1.0115272170402339</v>
       </c>
       <c r="AG38" s="5">
         <v>23414</v>
@@ -7033,14 +7033,14 @@
       </c>
       <c r="AI38" s="3">
         <f t="shared" si="42"/>
-        <v>8896</v>
+        <v>8897</v>
       </c>
       <c r="AJ38" s="5">
-        <v>23634</v>
+        <v>23635</v>
       </c>
       <c r="AK38" s="4">
         <f t="shared" si="43"/>
-        <v>1.0093960878107116</v>
+        <v>1.0094387973007601</v>
       </c>
       <c r="AL38" s="5">
         <v>23927</v>
@@ -7050,14 +7050,14 @@
       </c>
       <c r="AN38" s="3">
         <f t="shared" si="44"/>
-        <v>8958</v>
+        <v>8959</v>
       </c>
       <c r="AO38" s="5">
-        <v>23909</v>
+        <v>23910</v>
       </c>
       <c r="AP38" s="4">
         <f t="shared" si="45"/>
-        <v>0.99924771179002803</v>
+        <v>0.99928950557947094</v>
       </c>
       <c r="AQ38" s="5">
         <v>36551</v>
@@ -7067,14 +7067,14 @@
       </c>
       <c r="AS38" s="3">
         <f t="shared" si="46"/>
-        <v>13392</v>
+        <v>13394</v>
       </c>
       <c r="AT38" s="5">
-        <v>37090</v>
+        <v>37092</v>
       </c>
       <c r="AU38" s="4">
         <f t="shared" si="47"/>
-        <v>1.0147465185631037</v>
+        <v>1.0148012366282728</v>
       </c>
       <c r="AV38" s="5">
         <v>23833</v>
@@ -7084,14 +7084,14 @@
       </c>
       <c r="AX38" s="3">
         <f t="shared" si="48"/>
-        <v>8940</v>
+        <v>8943</v>
       </c>
       <c r="AY38" s="5">
-        <v>24144</v>
+        <v>24147</v>
       </c>
       <c r="AZ38" s="4">
         <f t="shared" si="49"/>
-        <v>1.0130491335543155</v>
+        <v>1.0131750094406915</v>
       </c>
       <c r="BA38" s="5">
         <v>24292</v>
@@ -7101,14 +7101,14 @@
       </c>
       <c r="BC38" s="3">
         <f t="shared" si="50"/>
-        <v>8903</v>
+        <v>8905</v>
       </c>
       <c r="BD38" s="5">
-        <v>24407</v>
+        <v>24409</v>
       </c>
       <c r="BE38" s="4">
         <f t="shared" si="51"/>
-        <v>1.0047340688292441</v>
+        <v>1.0048164004610571</v>
       </c>
       <c r="BF38" s="5">
         <v>37393</v>
@@ -7118,14 +7118,14 @@
       </c>
       <c r="BH38" s="3">
         <f t="shared" si="52"/>
-        <v>15246</v>
+        <v>15248</v>
       </c>
       <c r="BI38" s="5">
-        <v>37601</v>
+        <v>37603</v>
       </c>
       <c r="BJ38" s="4">
         <f t="shared" si="53"/>
-        <v>1.005562538443024</v>
+        <v>1.0056160243895917</v>
       </c>
     </row>
     <row r="39" spans="1:62" x14ac:dyDescent="0.3">
@@ -7355,14 +7355,14 @@
       </c>
       <c r="E40" s="3">
         <f t="shared" si="0"/>
-        <v>104871</v>
+        <v>104875</v>
       </c>
       <c r="F40" s="5">
-        <v>275855</v>
+        <v>275859</v>
       </c>
       <c r="G40" s="4">
         <f t="shared" si="1"/>
-        <v>0.99327745011198254</v>
+        <v>0.99329185300408318</v>
       </c>
       <c r="H40" s="5">
         <v>279588</v>
@@ -7372,14 +7372,14 @@
       </c>
       <c r="J40" s="3">
         <f t="shared" si="32"/>
-        <v>108071</v>
+        <v>108074</v>
       </c>
       <c r="K40" s="5">
-        <v>277560</v>
+        <v>277563</v>
       </c>
       <c r="L40" s="4">
         <f t="shared" si="33"/>
-        <v>0.99274646980557102</v>
+        <v>0.99275719987982314</v>
       </c>
       <c r="M40" s="5">
         <v>339205</v>
@@ -7389,14 +7389,14 @@
       </c>
       <c r="O40" s="3">
         <f t="shared" si="34"/>
-        <v>135137</v>
+        <v>135142</v>
       </c>
       <c r="P40" s="5">
-        <v>337539</v>
+        <v>337544</v>
       </c>
       <c r="Q40" s="4">
         <f t="shared" si="35"/>
-        <v>0.9950885157942837</v>
+        <v>0.99510325614304029</v>
       </c>
       <c r="R40" s="5">
         <v>280405</v>
@@ -7406,14 +7406,14 @@
       </c>
       <c r="T40" s="3">
         <f t="shared" si="36"/>
-        <v>104715</v>
+        <v>104719</v>
       </c>
       <c r="U40" s="5">
-        <v>278871</v>
+        <v>278875</v>
       </c>
       <c r="V40" s="4">
         <f t="shared" si="37"/>
-        <v>0.9945293414882046</v>
+        <v>0.9945436065690697</v>
       </c>
       <c r="W40" s="5">
         <v>283529</v>
@@ -7423,14 +7423,14 @@
       </c>
       <c r="Y40" s="3">
         <f t="shared" si="38"/>
-        <v>110251</v>
+        <v>110257</v>
       </c>
       <c r="Z40" s="5">
-        <v>280815</v>
+        <v>280821</v>
       </c>
       <c r="AA40" s="4">
         <f t="shared" si="39"/>
-        <v>0.99042778692832123</v>
+        <v>0.9904489487847804</v>
       </c>
       <c r="AB40" s="5">
         <v>342699</v>
@@ -7440,14 +7440,14 @@
       </c>
       <c r="AD40" s="3">
         <f t="shared" si="40"/>
-        <v>136256</v>
+        <v>136262</v>
       </c>
       <c r="AE40" s="5">
-        <v>341683</v>
+        <v>341689</v>
       </c>
       <c r="AF40" s="4">
         <f t="shared" si="41"/>
-        <v>0.99703529919842193</v>
+        <v>0.99705280727402179</v>
       </c>
       <c r="AG40" s="5">
         <v>284836</v>
@@ -7457,14 +7457,14 @@
       </c>
       <c r="AI40" s="3">
         <f t="shared" si="42"/>
-        <v>104293</v>
+        <v>104299</v>
       </c>
       <c r="AJ40" s="5">
-        <v>283424</v>
+        <v>283430</v>
       </c>
       <c r="AK40" s="4">
         <f t="shared" si="43"/>
-        <v>0.9950427614486933</v>
+        <v>0.99506382620174416</v>
       </c>
       <c r="AL40" s="5">
         <v>287465</v>
@@ -7474,14 +7474,14 @@
       </c>
       <c r="AN40" s="3">
         <f t="shared" si="44"/>
-        <v>109811</v>
+        <v>109820</v>
       </c>
       <c r="AO40" s="5">
-        <v>285654</v>
+        <v>285663</v>
       </c>
       <c r="AP40" s="4">
         <f t="shared" si="45"/>
-        <v>0.99370010262118869</v>
+        <v>0.9937314107804428</v>
       </c>
       <c r="AQ40" s="5">
         <v>346543</v>
@@ -7491,14 +7491,14 @@
       </c>
       <c r="AS40" s="3">
         <f t="shared" si="46"/>
-        <v>133833</v>
+        <v>133843</v>
       </c>
       <c r="AT40" s="5">
-        <v>346493</v>
+        <v>346503</v>
       </c>
       <c r="AU40" s="4">
         <f t="shared" si="47"/>
-        <v>0.99985571776085502</v>
+        <v>0.99988457420868404</v>
       </c>
       <c r="AV40" s="5">
         <v>288959</v>
@@ -7508,14 +7508,14 @@
       </c>
       <c r="AX40" s="3">
         <f t="shared" si="48"/>
-        <v>110681</v>
+        <v>110690</v>
       </c>
       <c r="AY40" s="5">
-        <v>287777</v>
+        <v>287786</v>
       </c>
       <c r="AZ40" s="4">
         <f t="shared" si="49"/>
-        <v>0.99590945428244149</v>
+        <v>0.99594060056963096</v>
       </c>
       <c r="BA40" s="5">
         <v>291465</v>
@@ -7525,14 +7525,14 @@
       </c>
       <c r="BC40" s="3">
         <f t="shared" si="50"/>
-        <v>109557</v>
+        <v>109568</v>
       </c>
       <c r="BD40" s="5">
-        <v>288957</v>
+        <v>288968</v>
       </c>
       <c r="BE40" s="4">
         <f t="shared" si="51"/>
-        <v>0.99139519324790282</v>
+        <v>0.99143293362839446</v>
       </c>
       <c r="BF40" s="5">
         <v>351557</v>
@@ -7542,14 +7542,14 @@
       </c>
       <c r="BH40" s="3">
         <f t="shared" si="52"/>
-        <v>149318</v>
+        <v>149331</v>
       </c>
       <c r="BI40" s="5">
-        <v>349467</v>
+        <v>349480</v>
       </c>
       <c r="BJ40" s="4">
         <f t="shared" si="53"/>
-        <v>0.99405501810517216</v>
+        <v>0.99409199646145574</v>
       </c>
     </row>
     <row r="41" spans="1:62" x14ac:dyDescent="0.3">
@@ -7567,14 +7567,14 @@
       </c>
       <c r="E41" s="3">
         <f t="shared" si="0"/>
-        <v>345446</v>
+        <v>345458</v>
       </c>
       <c r="F41" s="5">
-        <v>905572</v>
+        <v>905584</v>
       </c>
       <c r="G41" s="4">
         <f t="shared" si="1"/>
-        <v>0.99282765092959868</v>
+        <v>0.99284080717980427</v>
       </c>
       <c r="H41" s="5">
         <v>920596</v>
@@ -7584,14 +7584,14 @@
       </c>
       <c r="J41" s="3">
         <f t="shared" si="32"/>
-        <v>358278</v>
+        <v>358291</v>
       </c>
       <c r="K41" s="5">
-        <v>910585</v>
+        <v>910598</v>
       </c>
       <c r="L41" s="4">
         <f t="shared" si="33"/>
-        <v>0.98912552303073231</v>
+        <v>0.989139644317377</v>
       </c>
       <c r="M41" s="5">
         <v>1028922</v>
@@ -7601,14 +7601,14 @@
       </c>
       <c r="O41" s="3">
         <f t="shared" si="34"/>
-        <v>396227</v>
+        <v>396239</v>
       </c>
       <c r="P41" s="5">
-        <v>1018334</v>
+        <v>1018346</v>
       </c>
       <c r="Q41" s="4">
         <f t="shared" si="35"/>
-        <v>0.98970961841616756</v>
+        <v>0.98972128110780022</v>
       </c>
       <c r="R41" s="5">
         <v>924082</v>
@@ -7618,14 +7618,14 @@
       </c>
       <c r="T41" s="3">
         <f t="shared" si="36"/>
-        <v>360542</v>
+        <v>360554</v>
       </c>
       <c r="U41" s="5">
-        <v>915062</v>
+        <v>915074</v>
       </c>
       <c r="V41" s="4">
         <f t="shared" si="37"/>
-        <v>0.99023896147744461</v>
+        <v>0.99025194733800681</v>
       </c>
       <c r="W41" s="5">
         <v>929406</v>
@@ -7635,14 +7635,14 @@
       </c>
       <c r="Y41" s="3">
         <f t="shared" si="38"/>
-        <v>356214</v>
+        <v>356227</v>
       </c>
       <c r="Z41" s="5">
-        <v>919018</v>
+        <v>919031</v>
       </c>
       <c r="AA41" s="4">
         <f t="shared" si="39"/>
-        <v>0.98882296864879293</v>
+        <v>0.98883695607732247</v>
       </c>
       <c r="AB41" s="5">
         <v>1036539</v>
@@ -7652,14 +7652,14 @@
       </c>
       <c r="AD41" s="3">
         <f t="shared" si="40"/>
-        <v>396641</v>
+        <v>396662</v>
       </c>
       <c r="AE41" s="5">
-        <v>1027457</v>
+        <v>1027478</v>
       </c>
       <c r="AF41" s="4">
         <f t="shared" si="41"/>
-        <v>0.99123814926404119</v>
+        <v>0.99125840899377637</v>
       </c>
       <c r="AG41" s="5">
         <v>935526</v>
@@ -7669,14 +7669,14 @@
       </c>
       <c r="AI41" s="3">
         <f t="shared" si="42"/>
-        <v>348966</v>
+        <v>348985</v>
       </c>
       <c r="AJ41" s="5">
-        <v>925598</v>
+        <v>925617</v>
       </c>
       <c r="AK41" s="4">
         <f t="shared" si="43"/>
-        <v>0.98938778826029417</v>
+        <v>0.98940809769049709</v>
       </c>
       <c r="AL41" s="5">
         <v>940174</v>
@@ -7686,14 +7686,14 @@
       </c>
       <c r="AN41" s="3">
         <f t="shared" si="44"/>
-        <v>363762</v>
+        <v>363781</v>
       </c>
       <c r="AO41" s="5">
-        <v>930164</v>
+        <v>930183</v>
       </c>
       <c r="AP41" s="4">
         <f t="shared" si="45"/>
-        <v>0.98935303465103264</v>
+        <v>0.98937324367617063</v>
       </c>
       <c r="AQ41" s="5">
         <v>1046219</v>
@@ -7703,14 +7703,14 @@
       </c>
       <c r="AS41" s="3">
         <f t="shared" si="46"/>
-        <v>386077</v>
+        <v>386102</v>
       </c>
       <c r="AT41" s="5">
-        <v>1038964</v>
+        <v>1038989</v>
       </c>
       <c r="AU41" s="4">
         <f t="shared" si="47"/>
-        <v>0.99306550540565597</v>
+        <v>0.9930894009762774</v>
       </c>
       <c r="AV41" s="5">
         <v>945246</v>
@@ -7720,14 +7720,14 @@
       </c>
       <c r="AX41" s="3">
         <f t="shared" si="48"/>
-        <v>357518</v>
+        <v>357540</v>
       </c>
       <c r="AY41" s="5">
-        <v>936957</v>
+        <v>936979</v>
       </c>
       <c r="AZ41" s="4">
         <f t="shared" si="49"/>
-        <v>0.99123085419033774</v>
+        <v>0.9912541285548947</v>
       </c>
       <c r="BA41" s="5">
         <v>950318</v>
@@ -7737,14 +7737,14 @@
       </c>
       <c r="BC41" s="3">
         <f t="shared" si="50"/>
-        <v>355025</v>
+        <v>355049</v>
       </c>
       <c r="BD41" s="5">
-        <v>940900</v>
+        <v>940924</v>
       </c>
       <c r="BE41" s="4">
         <f t="shared" si="51"/>
-        <v>0.9900896331543757</v>
+        <v>0.99011488785859048</v>
       </c>
       <c r="BF41" s="5">
         <v>1056723</v>
@@ -7754,14 +7754,14 @@
       </c>
       <c r="BH41" s="3">
         <f t="shared" si="52"/>
-        <v>422026</v>
+        <v>422055</v>
       </c>
       <c r="BI41" s="5">
-        <v>1049266</v>
+        <v>1049295</v>
       </c>
       <c r="BJ41" s="4">
         <f t="shared" si="53"/>
-        <v>0.9929432784182799</v>
+        <v>0.99297072175016532</v>
       </c>
     </row>
     <row r="42" spans="1:62" x14ac:dyDescent="0.3">
@@ -7991,14 +7991,14 @@
       </c>
       <c r="E43" s="3">
         <f t="shared" si="0"/>
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="F43" s="5">
-        <v>3457</v>
+        <v>3458</v>
       </c>
       <c r="G43" s="4">
         <f t="shared" si="1"/>
-        <v>1.0005788712011578</v>
+        <v>1.0008683068017366</v>
       </c>
       <c r="H43" s="5">
         <v>3541</v>
@@ -8008,14 +8008,14 @@
       </c>
       <c r="J43" s="3">
         <f t="shared" si="32"/>
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="K43" s="5">
-        <v>3477</v>
+        <v>3478</v>
       </c>
       <c r="L43" s="4">
         <f t="shared" si="33"/>
-        <v>0.98192600960180743</v>
+        <v>0.98220841570177919</v>
       </c>
       <c r="M43" s="5">
         <v>4395</v>
@@ -8025,14 +8025,14 @@
       </c>
       <c r="O43" s="3">
         <f t="shared" si="34"/>
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="P43" s="5">
-        <v>4354</v>
+        <v>4355</v>
       </c>
       <c r="Q43" s="4">
         <f t="shared" si="35"/>
-        <v>0.99067121729237773</v>
+        <v>0.99089874857792948</v>
       </c>
       <c r="R43" s="5">
         <v>3498</v>
@@ -8042,14 +8042,14 @@
       </c>
       <c r="T43" s="3">
         <f t="shared" si="36"/>
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="U43" s="5">
-        <v>3493</v>
+        <v>3494</v>
       </c>
       <c r="V43" s="4">
         <f t="shared" si="37"/>
-        <v>0.99857061177815898</v>
+        <v>0.99885648942252714</v>
       </c>
       <c r="W43" s="5">
         <v>3551</v>
@@ -8059,14 +8059,14 @@
       </c>
       <c r="Y43" s="3">
         <f t="shared" si="38"/>
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="Z43" s="5">
-        <v>3520</v>
+        <v>3521</v>
       </c>
       <c r="AA43" s="4">
         <f t="shared" si="39"/>
-        <v>0.99127006477048718</v>
+        <v>0.99155167558434243</v>
       </c>
       <c r="AB43" s="5">
         <v>4429</v>
@@ -8076,14 +8076,14 @@
       </c>
       <c r="AD43" s="3">
         <f t="shared" si="40"/>
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="AE43" s="5">
-        <v>4391</v>
+        <v>4392</v>
       </c>
       <c r="AF43" s="4">
         <f t="shared" si="41"/>
-        <v>0.99142018514337327</v>
+        <v>0.99164596974486341</v>
       </c>
       <c r="AG43" s="5">
         <v>3560</v>
@@ -8093,14 +8093,14 @@
       </c>
       <c r="AI43" s="3">
         <f t="shared" si="42"/>
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="AJ43" s="5">
-        <v>3546</v>
+        <v>3547</v>
       </c>
       <c r="AK43" s="4">
         <f t="shared" si="43"/>
-        <v>0.99606741573033708</v>
+        <v>0.99634831460674156</v>
       </c>
       <c r="AL43" s="5">
         <v>3588</v>
@@ -8110,14 +8110,14 @@
       </c>
       <c r="AN43" s="3">
         <f t="shared" si="44"/>
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="AO43" s="5">
-        <v>3581</v>
+        <v>3582</v>
       </c>
       <c r="AP43" s="4">
         <f t="shared" si="45"/>
-        <v>0.99804905239687847</v>
+        <v>0.99832775919732442</v>
       </c>
       <c r="AQ43" s="5">
         <v>4449</v>
@@ -8127,14 +8127,14 @@
       </c>
       <c r="AS43" s="3">
         <f t="shared" si="46"/>
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="AT43" s="5">
-        <v>4470</v>
+        <v>4471</v>
       </c>
       <c r="AU43" s="4">
         <f t="shared" si="47"/>
-        <v>1.0047201618341199</v>
+        <v>1.0049449314452685</v>
       </c>
       <c r="AV43" s="5">
         <v>3616</v>
@@ -8144,14 +8144,14 @@
       </c>
       <c r="AX43" s="3">
         <f t="shared" si="48"/>
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="AY43" s="5">
-        <v>3632</v>
+        <v>3633</v>
       </c>
       <c r="AZ43" s="4">
         <f t="shared" si="49"/>
-        <v>1.0044247787610618</v>
+        <v>1.0047013274336283</v>
       </c>
       <c r="BA43" s="5">
         <v>3655</v>
@@ -8161,14 +8161,14 @@
       </c>
       <c r="BC43" s="3">
         <f t="shared" si="50"/>
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="BD43" s="5">
-        <v>3655</v>
+        <v>3656</v>
       </c>
       <c r="BE43" s="4">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>1.0002735978112176</v>
       </c>
       <c r="BF43" s="5">
         <v>4544</v>
@@ -8178,14 +8178,14 @@
       </c>
       <c r="BH43" s="3">
         <f t="shared" si="52"/>
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="BI43" s="5">
-        <v>4551</v>
+        <v>4552</v>
       </c>
       <c r="BJ43" s="4">
         <f t="shared" si="53"/>
-        <v>1.0015404929577465</v>
+        <v>1.0017605633802817</v>
       </c>
     </row>
     <row r="44" spans="1:62" x14ac:dyDescent="0.3">
@@ -8203,14 +8203,14 @@
       </c>
       <c r="E44" s="3">
         <f t="shared" si="0"/>
-        <v>164131</v>
+        <v>164132</v>
       </c>
       <c r="F44" s="5">
-        <v>333699</v>
+        <v>333700</v>
       </c>
       <c r="G44" s="4">
         <f t="shared" si="1"/>
-        <v>0.99247831828402155</v>
+        <v>0.99248129245630945</v>
       </c>
       <c r="H44" s="5">
         <v>340996</v>
@@ -8237,14 +8237,14 @@
       </c>
       <c r="O44" s="3">
         <f t="shared" si="34"/>
-        <v>200402</v>
+        <v>200403</v>
       </c>
       <c r="P44" s="5">
-        <v>404898</v>
+        <v>404899</v>
       </c>
       <c r="Q44" s="4">
         <f t="shared" si="35"/>
-        <v>0.9911532586558045</v>
+        <v>0.9911557065643114</v>
       </c>
       <c r="R44" s="5">
         <v>342556</v>
@@ -8254,14 +8254,14 @@
       </c>
       <c r="T44" s="3">
         <f t="shared" si="36"/>
-        <v>167628</v>
+        <v>167630</v>
       </c>
       <c r="U44" s="5">
-        <v>339659</v>
+        <v>339661</v>
       </c>
       <c r="V44" s="4">
         <f t="shared" si="37"/>
-        <v>0.99154298859164636</v>
+        <v>0.99154882705309499</v>
       </c>
       <c r="W44" s="5">
         <v>347597</v>
@@ -8271,14 +8271,14 @@
       </c>
       <c r="Y44" s="3">
         <f t="shared" si="38"/>
-        <v>168816</v>
+        <v>168818</v>
       </c>
       <c r="Z44" s="5">
-        <v>343540</v>
+        <v>343542</v>
       </c>
       <c r="AA44" s="4">
         <f t="shared" si="39"/>
-        <v>0.98832843781735746</v>
+        <v>0.98833419160694713</v>
       </c>
       <c r="AB44" s="5">
         <v>416340</v>
@@ -8288,14 +8288,14 @@
       </c>
       <c r="AD44" s="3">
         <f t="shared" si="40"/>
-        <v>203196</v>
+        <v>203200</v>
       </c>
       <c r="AE44" s="5">
-        <v>413221</v>
+        <v>413225</v>
       </c>
       <c r="AF44" s="4">
         <f t="shared" si="41"/>
-        <v>0.99250852668492096</v>
+        <v>0.99251813421722634</v>
       </c>
       <c r="AG44" s="5">
         <v>350469</v>
@@ -8305,14 +8305,14 @@
       </c>
       <c r="AI44" s="3">
         <f t="shared" si="42"/>
-        <v>166211</v>
+        <v>166216</v>
       </c>
       <c r="AJ44" s="5">
-        <v>347636</v>
+        <v>347641</v>
       </c>
       <c r="AK44" s="4">
         <f t="shared" si="43"/>
-        <v>0.99191654611392166</v>
+        <v>0.99193081271096728</v>
       </c>
       <c r="AL44" s="5">
         <v>355186</v>
@@ -8322,14 +8322,14 @@
       </c>
       <c r="AN44" s="3">
         <f t="shared" si="44"/>
-        <v>169382</v>
+        <v>169387</v>
       </c>
       <c r="AO44" s="5">
-        <v>351115</v>
+        <v>351120</v>
       </c>
       <c r="AP44" s="4">
         <f t="shared" si="45"/>
-        <v>0.9885383995990833</v>
+        <v>0.98855247673050173</v>
       </c>
       <c r="AQ44" s="5">
         <v>424208</v>
@@ -8339,14 +8339,14 @@
       </c>
       <c r="AS44" s="3">
         <f t="shared" si="46"/>
-        <v>198297</v>
+        <v>198304</v>
       </c>
       <c r="AT44" s="5">
-        <v>421884</v>
+        <v>421891</v>
       </c>
       <c r="AU44" s="4">
         <f t="shared" si="47"/>
-        <v>0.99452155546335763</v>
+        <v>0.99453805680232343</v>
       </c>
       <c r="AV44" s="5">
         <v>358114</v>
@@ -8356,14 +8356,14 @@
       </c>
       <c r="AX44" s="3">
         <f t="shared" si="48"/>
-        <v>167159</v>
+        <v>167164</v>
       </c>
       <c r="AY44" s="5">
-        <v>354720</v>
+        <v>354725</v>
       </c>
       <c r="AZ44" s="4">
         <f t="shared" si="49"/>
-        <v>0.99052257102486918</v>
+        <v>0.99053653305930511</v>
       </c>
       <c r="BA44" s="5">
         <v>361984</v>
@@ -8373,14 +8373,14 @@
       </c>
       <c r="BC44" s="3">
         <f t="shared" si="50"/>
-        <v>170870</v>
+        <v>170876</v>
       </c>
       <c r="BD44" s="5">
-        <v>357821</v>
+        <v>357827</v>
       </c>
       <c r="BE44" s="4">
         <f t="shared" si="51"/>
-        <v>0.98849949169024043</v>
+        <v>0.9885160670084866</v>
       </c>
       <c r="BF44" s="5">
         <v>432310</v>
@@ -8390,14 +8390,14 @@
       </c>
       <c r="BH44" s="3">
         <f t="shared" si="52"/>
-        <v>225482</v>
+        <v>225489</v>
       </c>
       <c r="BI44" s="5">
-        <v>428078</v>
+        <v>428085</v>
       </c>
       <c r="BJ44" s="4">
         <f t="shared" si="53"/>
-        <v>0.99021072841248181</v>
+        <v>0.99022692049686567</v>
       </c>
     </row>
     <row r="45" spans="1:62" x14ac:dyDescent="0.3">
@@ -8415,14 +8415,14 @@
       </c>
       <c r="E45" s="3">
         <f t="shared" si="0"/>
-        <v>116368</v>
+        <v>116371</v>
       </c>
       <c r="F45" s="5">
-        <v>251481</v>
+        <v>251484</v>
       </c>
       <c r="G45" s="4">
         <f t="shared" si="1"/>
-        <v>0.98404667433615856</v>
+        <v>0.98405841335430699</v>
       </c>
       <c r="H45" s="5">
         <v>257610</v>
@@ -8432,14 +8432,14 @@
       </c>
       <c r="J45" s="3">
         <f t="shared" si="32"/>
-        <v>119223</v>
+        <v>119226</v>
       </c>
       <c r="K45" s="5">
-        <v>253406</v>
+        <v>253409</v>
       </c>
       <c r="L45" s="4">
         <f t="shared" si="33"/>
-        <v>0.98368075773455999</v>
+        <v>0.98369240324521567</v>
       </c>
       <c r="M45" s="5">
         <v>310366</v>
@@ -8449,14 +8449,14 @@
       </c>
       <c r="O45" s="3">
         <f t="shared" si="34"/>
-        <v>144182</v>
+        <v>144185</v>
       </c>
       <c r="P45" s="5">
-        <v>305416</v>
+        <v>305419</v>
       </c>
       <c r="Q45" s="4">
         <f t="shared" si="35"/>
-        <v>0.98405108807021391</v>
+        <v>0.98406075407744409</v>
       </c>
       <c r="R45" s="5">
         <v>257356</v>
@@ -8466,14 +8466,14 @@
       </c>
       <c r="T45" s="3">
         <f t="shared" si="36"/>
-        <v>118791</v>
+        <v>118794</v>
       </c>
       <c r="U45" s="5">
-        <v>253933</v>
+        <v>253936</v>
       </c>
       <c r="V45" s="4">
         <f t="shared" si="37"/>
-        <v>0.98669935808762954</v>
+        <v>0.98671101509193493</v>
       </c>
       <c r="W45" s="5">
         <v>260553</v>
@@ -8483,14 +8483,14 @@
       </c>
       <c r="Y45" s="3">
         <f t="shared" si="38"/>
-        <v>120995</v>
+        <v>120999</v>
       </c>
       <c r="Z45" s="5">
-        <v>255896</v>
+        <v>255900</v>
       </c>
       <c r="AA45" s="4">
         <f t="shared" si="39"/>
-        <v>0.98212647714668422</v>
+        <v>0.98214182910962455</v>
       </c>
       <c r="AB45" s="5">
         <v>313911</v>
@@ -8500,14 +8500,14 @@
       </c>
       <c r="AD45" s="3">
         <f t="shared" si="40"/>
-        <v>148043</v>
+        <v>148050</v>
       </c>
       <c r="AE45" s="5">
-        <v>309037</v>
+        <v>309044</v>
       </c>
       <c r="AF45" s="4">
         <f t="shared" si="41"/>
-        <v>0.98447330612817008</v>
+        <v>0.98449560544230685</v>
       </c>
       <c r="AG45" s="5">
         <v>261210</v>
@@ -8517,14 +8517,14 @@
       </c>
       <c r="AI45" s="3">
         <f t="shared" si="42"/>
-        <v>116300</v>
+        <v>116305</v>
       </c>
       <c r="AJ45" s="5">
-        <v>257224</v>
+        <v>257229</v>
       </c>
       <c r="AK45" s="4">
         <f t="shared" si="43"/>
-        <v>0.98474024731059306</v>
+        <v>0.98475938899735849</v>
       </c>
       <c r="AL45" s="5">
         <v>264020</v>
@@ -8534,14 +8534,14 @@
       </c>
       <c r="AN45" s="3">
         <f t="shared" si="44"/>
-        <v>120924</v>
+        <v>120931</v>
       </c>
       <c r="AO45" s="5">
-        <v>259618</v>
+        <v>259625</v>
       </c>
       <c r="AP45" s="4">
         <f t="shared" si="45"/>
-        <v>0.98332702068025146</v>
+        <v>0.98335353382319524</v>
       </c>
       <c r="AQ45" s="5">
         <v>317407</v>
@@ -8551,14 +8551,14 @@
       </c>
       <c r="AS45" s="3">
         <f t="shared" si="46"/>
-        <v>143510</v>
+        <v>143520</v>
       </c>
       <c r="AT45" s="5">
-        <v>312048</v>
+        <v>312058</v>
       </c>
       <c r="AU45" s="4">
         <f t="shared" si="47"/>
-        <v>0.98311631438500091</v>
+        <v>0.98314781967631459</v>
       </c>
       <c r="AV45" s="5">
         <v>263886</v>
@@ -8568,14 +8568,14 @@
       </c>
       <c r="AX45" s="3">
         <f t="shared" si="48"/>
-        <v>118320</v>
+        <v>118328</v>
       </c>
       <c r="AY45" s="5">
-        <v>259622</v>
+        <v>259630</v>
       </c>
       <c r="AZ45" s="4">
         <f t="shared" si="49"/>
-        <v>0.98384150731755382</v>
+        <v>0.98387182343890922</v>
       </c>
       <c r="BA45" s="5">
         <v>265781</v>
@@ -8585,14 +8585,14 @@
       </c>
       <c r="BC45" s="3">
         <f t="shared" si="50"/>
-        <v>120905</v>
+        <v>120912</v>
       </c>
       <c r="BD45" s="5">
-        <v>261451</v>
+        <v>261458</v>
       </c>
       <c r="BE45" s="4">
         <f t="shared" si="51"/>
-        <v>0.98370839149525358</v>
+        <v>0.98373472896858694</v>
       </c>
       <c r="BF45" s="5">
         <v>319799</v>
@@ -8602,14 +8602,14 @@
       </c>
       <c r="BH45" s="3">
         <f t="shared" si="52"/>
-        <v>165114</v>
+        <v>165124</v>
       </c>
       <c r="BI45" s="5">
-        <v>315179</v>
+        <v>315189</v>
       </c>
       <c r="BJ45" s="4">
         <f t="shared" si="53"/>
-        <v>0.98555342574554639</v>
+        <v>0.98558469538678983</v>
       </c>
     </row>
     <row r="46" spans="1:62" x14ac:dyDescent="0.3">
@@ -9037,10 +9037,10 @@
       </c>
     </row>
     <row r="48" spans="1:62" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
+      <c r="A48" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="B48" s="18"/>
+      <c r="B48" s="14"/>
       <c r="C48" s="7">
         <f>SUM(C10:C47)</f>
         <v>7712416</v>
@@ -9051,15 +9051,15 @@
       </c>
       <c r="E48" s="8">
         <f>F48-D48</f>
-        <v>3007798</v>
+        <v>3007877</v>
       </c>
       <c r="F48" s="7">
         <f>SUM(F10:F47)</f>
-        <v>7666727</v>
+        <v>7666806</v>
       </c>
       <c r="G48" s="6">
         <f>F48/C48</f>
-        <v>0.9940759160294258</v>
+        <v>0.9940861592528204</v>
       </c>
       <c r="H48" s="7">
         <f>SUM(H10:H47)</f>
@@ -9071,15 +9071,15 @@
       </c>
       <c r="J48" s="8">
         <f>K48-I48</f>
-        <v>3058445</v>
+        <v>3058532</v>
       </c>
       <c r="K48" s="7">
         <f>SUM(K10:K47)</f>
-        <v>7765300</v>
+        <v>7765387</v>
       </c>
       <c r="L48" s="6">
         <f>K48/H48</f>
-        <v>0.98702942187350651</v>
+        <v>0.98704048024339597</v>
       </c>
       <c r="M48" s="7">
         <f>SUM(M10:M47)</f>
@@ -9091,15 +9091,15 @@
       </c>
       <c r="O48" s="8">
         <f>P48-N48</f>
-        <v>4954715</v>
+        <v>4954825</v>
       </c>
       <c r="P48" s="7">
         <f>SUM(P10:P47)</f>
-        <v>12077379</v>
+        <v>12077489</v>
       </c>
       <c r="Q48" s="6">
         <f>P48/M48</f>
-        <v>0.99383875515418874</v>
+        <v>0.99384780697437813</v>
       </c>
       <c r="R48" s="7">
         <f>SUM(R10:R47)</f>
@@ -9111,15 +9111,15 @@
       </c>
       <c r="T48" s="8">
         <f>U48-S48</f>
-        <v>3023388</v>
+        <v>3023485</v>
       </c>
       <c r="U48" s="7">
         <f>SUM(U10:U47)</f>
-        <v>7734752</v>
+        <v>7734849</v>
       </c>
       <c r="V48" s="6">
         <f>U48/R48</f>
-        <v>0.99088624453345697</v>
+        <v>0.99089867104250595</v>
       </c>
       <c r="W48" s="7">
         <f>SUM(W10:W47)</f>
@@ -9131,15 +9131,15 @@
       </c>
       <c r="Y48" s="8">
         <f>Z48-X48</f>
-        <v>3062791</v>
+        <v>3062902</v>
       </c>
       <c r="Z48" s="7">
         <f>SUM(Z10:Z47)</f>
-        <v>7826496</v>
+        <v>7826607</v>
       </c>
       <c r="AA48" s="6">
         <f>Z48/W48</f>
-        <v>0.98473357070627199</v>
+        <v>0.98474753678078963</v>
       </c>
       <c r="AB48" s="7">
         <f>SUM(AB10:AB47)</f>
@@ -9151,15 +9151,15 @@
       </c>
       <c r="AD48" s="8">
         <f>AE48-AC48</f>
-        <v>4962849</v>
+        <v>4963035</v>
       </c>
       <c r="AE48" s="7">
         <f>SUM(AE10:AE47)</f>
-        <v>12221303</v>
+        <v>12221489</v>
       </c>
       <c r="AF48" s="6">
         <f>AE48/AB48</f>
-        <v>0.99488154641836468</v>
+        <v>0.99489668784539853</v>
       </c>
       <c r="AG48" s="7">
         <f>SUM(AG10:AG47)</f>
@@ -9171,15 +9171,15 @@
       </c>
       <c r="AI48" s="8">
         <f>AJ48-AH48</f>
-        <v>2974522</v>
+        <v>2974680</v>
       </c>
       <c r="AJ48" s="7">
         <f>SUM(AJ10:AJ47)</f>
-        <v>7866702</v>
+        <v>7866860</v>
       </c>
       <c r="AK48" s="6">
         <f>AJ48/AG48</f>
-        <v>0.99146953526082549</v>
+        <v>0.99148944858493149</v>
       </c>
       <c r="AL48" s="7">
         <f>SUM(AL10:AL47)</f>
@@ -9191,15 +9191,15 @@
       </c>
       <c r="AN48" s="8">
         <f>AO48-AM48</f>
-        <v>3044602</v>
+        <v>3044779</v>
       </c>
       <c r="AO48" s="7">
         <f>SUM(AO10:AO47)</f>
-        <v>7955732</v>
+        <v>7955909</v>
       </c>
       <c r="AP48" s="6">
         <f>AO48/AL48</f>
-        <v>0.98480592319567162</v>
+        <v>0.98482783326609702</v>
       </c>
       <c r="AQ48" s="7">
         <f>SUM(AQ10:AQ47)</f>
@@ -9211,15 +9211,15 @@
       </c>
       <c r="AS48" s="8">
         <f>AT48-AR48</f>
-        <v>4874311</v>
+        <v>4874598</v>
       </c>
       <c r="AT48" s="7">
         <f>SUM(AT10:AT47)</f>
-        <v>12411629</v>
+        <v>12411916</v>
       </c>
       <c r="AU48" s="6">
         <f>AT48/AQ48</f>
-        <v>0.99729880791428305</v>
+        <v>0.99732186892890662</v>
       </c>
       <c r="AV48" s="7">
         <f>SUM(AV10:AV47)</f>
@@ -9231,15 +9231,15 @@
       </c>
       <c r="AX48" s="8">
         <f>AY48-AW48</f>
-        <v>2995556</v>
+        <v>2995768</v>
       </c>
       <c r="AY48" s="7">
         <f>SUM(AY10:AY47)</f>
-        <v>8002469</v>
+        <v>8002681</v>
       </c>
       <c r="AZ48" s="6">
         <f>AY48/AV48</f>
-        <v>0.99269761240568566</v>
+        <v>0.9927239107760798</v>
       </c>
       <c r="BA48" s="7">
         <f>SUM(BA10:BA47)</f>
@@ -9251,15 +9251,15 @@
       </c>
       <c r="BC48" s="8">
         <f>BD48-BB48</f>
-        <v>3029331</v>
+        <v>3029567</v>
       </c>
       <c r="BD48" s="7">
         <f>SUM(BD10:BD47)</f>
-        <v>8095730</v>
+        <v>8095966</v>
       </c>
       <c r="BE48" s="6">
         <f>BD48/BA48</f>
-        <v>0.98698865156834148</v>
+        <v>0.98701742344212795</v>
       </c>
       <c r="BF48" s="7">
         <f>SUM(BF10:BF47)</f>
@@ -9271,25 +9271,19 @@
       </c>
       <c r="BH48" s="8">
         <f>BI48-BG48</f>
-        <v>5326723</v>
+        <v>5327135</v>
       </c>
       <c r="BI48" s="7">
         <f>SUM(BI10:BI47)</f>
-        <v>12583318</v>
+        <v>12583730</v>
       </c>
       <c r="BJ48" s="6">
         <f>BI48/BF48</f>
-        <v>0.99425239766562423</v>
+        <v>0.99428495124074945</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:G8"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="AQ8:AU8"/>
     <mergeCell ref="AV8:AZ8"/>
@@ -9302,6 +9296,12 @@
     <mergeCell ref="AG8:AK8"/>
     <mergeCell ref="AL8:AP8"/>
     <mergeCell ref="BA8:BE8"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
